--- a/data/import/ANNEX.xlsx
+++ b/data/import/ANNEX.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD9C543-116A-4FF9-BD77-291DD2AAC994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FD652A-C4E7-49D7-8A37-4D47F8CD2A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAC" sheetId="2" r:id="rId1"/>
@@ -13,13 +13,17 @@
     <sheet name="4AM" sheetId="3" r:id="rId3"/>
     <sheet name="3AM" sheetId="6" r:id="rId4"/>
     <sheet name="2AM" sheetId="7" r:id="rId5"/>
+    <sheet name="1AM" sheetId="8" r:id="rId6"/>
+    <sheet name="5AP" sheetId="9" r:id="rId7"/>
+    <sheet name="4AP" sheetId="10" r:id="rId8"/>
+    <sheet name="3AP" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="785">
   <si>
     <t>الاسم واللقب</t>
   </si>
@@ -1987,6 +1991,393 @@
   </si>
   <si>
     <t>BON08(06/10/2026)</t>
+  </si>
+  <si>
+    <t>عميرش 1AM</t>
+  </si>
+  <si>
+    <t>حركاتي جواد</t>
+  </si>
+  <si>
+    <t>BON04(06/10/2026)</t>
+  </si>
+  <si>
+    <t>بن هلال ياسمين</t>
+  </si>
+  <si>
+    <t>BON02(06/10/2026)</t>
+  </si>
+  <si>
+    <t>بن عزوز 1 متوسط</t>
+  </si>
+  <si>
+    <t>حيمد محمد مهدي</t>
+  </si>
+  <si>
+    <t>07 70243227</t>
+  </si>
+  <si>
+    <t>BON01(01/10/2026)</t>
+  </si>
+  <si>
+    <t>5 ابتدائي رياضيات</t>
+  </si>
+  <si>
+    <t>الكنز لجين</t>
+  </si>
+  <si>
+    <t>06 60 51 31 68</t>
+  </si>
+  <si>
+    <t>BON 01(17/08/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يزيد خليل </t>
+  </si>
+  <si>
+    <t>0798 72 14 00/0782 86 30 88</t>
+  </si>
+  <si>
+    <t>BON 02(07/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 12(18/09/2026)</t>
+  </si>
+  <si>
+    <t>بومحراث جينان مارية</t>
+  </si>
+  <si>
+    <t>BON 04(15/09/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بلزرق يوسف </t>
+  </si>
+  <si>
+    <t>BON 05(15/09/2026)</t>
+  </si>
+  <si>
+    <t>بوالحوت امجد</t>
+  </si>
+  <si>
+    <t>BON 06(16/09/2026)</t>
+  </si>
+  <si>
+    <t>بوالقرع ميلسا</t>
+  </si>
+  <si>
+    <t>07 70340943/07 74717459</t>
+  </si>
+  <si>
+    <t>BON 07(18/09/2026)</t>
+  </si>
+  <si>
+    <t>حمادي سجود</t>
+  </si>
+  <si>
+    <t>BON 08(18/09/2026)</t>
+  </si>
+  <si>
+    <t>قلي محمد</t>
+  </si>
+  <si>
+    <t>BON 09(18/09/2026)</t>
+  </si>
+  <si>
+    <t>غولة ميراس</t>
+  </si>
+  <si>
+    <t>BON11(18/09/2026)</t>
+  </si>
+  <si>
+    <t>معمري ميسم</t>
+  </si>
+  <si>
+    <t>BON13(18/09/2026)</t>
+  </si>
+  <si>
+    <t>زغدود مبارك طهى</t>
+  </si>
+  <si>
+    <t>06 70187705/06 58614129</t>
+  </si>
+  <si>
+    <t>BON14(18/09/2026)</t>
+  </si>
+  <si>
+    <t>مشارة يوسف</t>
+  </si>
+  <si>
+    <t>BON21(18/09/2026)</t>
+  </si>
+  <si>
+    <t>شرقي محمد رائد</t>
+  </si>
+  <si>
+    <t>BON22(24/09/2026)</t>
+  </si>
+  <si>
+    <t>بوحلاس رحمة اميمة</t>
+  </si>
+  <si>
+    <t>BON23(24/09/2026)</t>
+  </si>
+  <si>
+    <t>جعوط تسنيم</t>
+  </si>
+  <si>
+    <t>BON 24(25/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 31(02/10/2026)</t>
+  </si>
+  <si>
+    <t>عبد الرزاق اسلام</t>
+  </si>
+  <si>
+    <t>BON 29(02/10/2026)</t>
+  </si>
+  <si>
+    <t>محتوم جود</t>
+  </si>
+  <si>
+    <t>BON 30(02/10/2026)</t>
+  </si>
+  <si>
+    <t>لبيض اياد</t>
+  </si>
+  <si>
+    <t>BON 32(02/10/2026)</t>
+  </si>
+  <si>
+    <t>5 ابتدائي لغة عربية</t>
+  </si>
+  <si>
+    <t>لبيض اياد امجد</t>
+  </si>
+  <si>
+    <t>0554 01 09 35/0550 96 92 60</t>
+  </si>
+  <si>
+    <t>0656 25 12 40</t>
+  </si>
+  <si>
+    <t>0776 62 30 59/0781 57 01 21</t>
+  </si>
+  <si>
+    <t>0672 52 80 97</t>
+  </si>
+  <si>
+    <t>0673 53 59 18/0668 25 72 81</t>
+  </si>
+  <si>
+    <t>0659 17 24 43/0779 83 87 06</t>
+  </si>
+  <si>
+    <t>BON 02(17/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 11(18/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 13(18/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 14(18/09/2026)</t>
+  </si>
+  <si>
+    <t>BON24(22/09/2026)</t>
+  </si>
+  <si>
+    <t>BON 34(02/10/2026)</t>
+  </si>
+  <si>
+    <t>بن عزوز 5 ابتدائي</t>
+  </si>
+  <si>
+    <t>BON 10(18/08/2026)</t>
+  </si>
+  <si>
+    <t>تليلي دعاء</t>
+  </si>
+  <si>
+    <t>0791 44 05 20/0699 66 11 14</t>
+  </si>
+  <si>
+    <t>BON 26(26/09/2026)</t>
+  </si>
+  <si>
+    <t>عليوة فادي</t>
+  </si>
+  <si>
+    <t>BON 27(26/09/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمير  عبد المهيمن </t>
+  </si>
+  <si>
+    <t>BON 28(29/09/2026)</t>
+  </si>
+  <si>
+    <t>بوديدة عبد السلام</t>
+  </si>
+  <si>
+    <t>BON 33(02/10/2026)</t>
+  </si>
+  <si>
+    <t>BON 35(02/10/2026)</t>
+  </si>
+  <si>
+    <t>شريبي لجين</t>
+  </si>
+  <si>
+    <t>BON 36(03/10/2026)</t>
+  </si>
+  <si>
+    <t>مروة 5 ابتدائي</t>
+  </si>
+  <si>
+    <t>يزيد خليل</t>
+  </si>
+  <si>
+    <t>BON 38(04/10/2026)</t>
+  </si>
+  <si>
+    <t>BON 10(18/09/2026)</t>
+  </si>
+  <si>
+    <t>جعطوط تسنيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تليلي دعاء </t>
+  </si>
+  <si>
+    <t>BON37(4/10/2026)</t>
+  </si>
+  <si>
+    <t>مروك ادم</t>
+  </si>
+  <si>
+    <t>BON39(4/10/2026)</t>
+  </si>
+  <si>
+    <t>4 ابتدائي لغة عربية</t>
+  </si>
+  <si>
+    <t>حيمد أمير</t>
+  </si>
+  <si>
+    <t>BON 52/3as(07/09/2026)</t>
+  </si>
+  <si>
+    <t>بوبكر عبد الرحمان</t>
+  </si>
+  <si>
+    <t>BON 53/3as(07/09/2026)</t>
+  </si>
+  <si>
+    <t>بوحلاسة مجيب الرحمان</t>
+  </si>
+  <si>
+    <t>BON 54/3as(07/09/2026)</t>
+  </si>
+  <si>
+    <t>زردازي عبد الودود</t>
+  </si>
+  <si>
+    <t>BON 01(19/09/2026)</t>
+  </si>
+  <si>
+    <t>بوعافي براء</t>
+  </si>
+  <si>
+    <t>06 99753989</t>
+  </si>
+  <si>
+    <t>BON 02(22/09/2026)</t>
+  </si>
+  <si>
+    <t>بن محمد ياسر</t>
+  </si>
+  <si>
+    <t>BON 03(25/09/2026)</t>
+  </si>
+  <si>
+    <t>ومان نيزار</t>
+  </si>
+  <si>
+    <t>05 60908908</t>
+  </si>
+  <si>
+    <t>BON 05(25/09/2026)</t>
+  </si>
+  <si>
+    <t>حركات تيم</t>
+  </si>
+  <si>
+    <t>BON 07(02/10/2026)</t>
+  </si>
+  <si>
+    <t>بن فطيمة يحي وليد</t>
+  </si>
+  <si>
+    <t>BON 08(02/10/2026)</t>
+  </si>
+  <si>
+    <t>فيلالي جوري أسماء</t>
+  </si>
+  <si>
+    <t>BON 09(02/10/2026)</t>
+  </si>
+  <si>
+    <t>غراب ياسمين</t>
+  </si>
+  <si>
+    <t>BON 10(02/10/2026)</t>
+  </si>
+  <si>
+    <t>4 ابتدائي رياضيات</t>
+  </si>
+  <si>
+    <t>بن عزوز 4 ابتدائي</t>
+  </si>
+  <si>
+    <t>BON02(22/092026)</t>
+  </si>
+  <si>
+    <t>BON04(25/092026)</t>
+  </si>
+  <si>
+    <t>نموشي مريم جنى</t>
+  </si>
+  <si>
+    <t>BON 06(30/09/2026)</t>
+  </si>
+  <si>
+    <t>3 ابتدائي لغة عربية</t>
+  </si>
+  <si>
+    <t>بركان بهاء الدين</t>
+  </si>
+  <si>
+    <t>بيدي يحي احمد</t>
+  </si>
+  <si>
+    <t>BON 02(21/09/2026)</t>
+  </si>
+  <si>
+    <t>دولة انس نجم الدين</t>
+  </si>
+  <si>
+    <t>BON 03(02/10/2026)</t>
+  </si>
+  <si>
+    <t>بوفندي محمد الإسلام</t>
+  </si>
+  <si>
+    <t>BON 04(02/10/2026)</t>
+  </si>
+  <si>
+    <t>3 ابتدائي رياضيات</t>
   </si>
 </sst>
 </file>
@@ -12635,4 +13026,3230 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6C7AE0-3130-40DD-BF4E-D974E3CC618F}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7">
+        <v>250</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13">
+        <v>250</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1500</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="C13" s="7">
+        <v>250</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1500</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58430E14-9518-4E22-9079-0ACEE1858FC0}">
+  <dimension ref="A1:I117"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="4" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C6" s="13">
+        <v>250</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13">
+        <v>250</v>
+      </c>
+      <c r="D8" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13">
+        <v>250</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13">
+        <v>250</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="C14" s="13">
+        <v>250</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>682</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13">
+        <v>250</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13">
+        <v>250</v>
+      </c>
+      <c r="D18" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13">
+        <v>250</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13">
+        <v>250</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="C24" s="13">
+        <v>250</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13">
+        <v>250</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>697</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13">
+        <v>250</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>699</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13">
+        <v>250</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13">
+        <v>250</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13">
+        <v>250</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="15"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="19"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C45" s="7">
+        <v>250</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C47" s="13">
+        <v>250</v>
+      </c>
+      <c r="D47" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="C49" s="13">
+        <v>250</v>
+      </c>
+      <c r="D49" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13">
+        <v>250</v>
+      </c>
+      <c r="D51" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="C53" s="13">
+        <v>250</v>
+      </c>
+      <c r="D53" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="15"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="C55" s="13">
+        <v>250</v>
+      </c>
+      <c r="D55" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="15"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
+        <v>682</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" s="13">
+        <v>250</v>
+      </c>
+      <c r="D57" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="13">
+        <v>250</v>
+      </c>
+      <c r="D59" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="15"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="B61" s="12"/>
+      <c r="C61" s="13">
+        <v>250</v>
+      </c>
+      <c r="D61" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="15"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="C63" s="13">
+        <v>250</v>
+      </c>
+      <c r="D63" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="15"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="C65" s="13">
+        <v>250</v>
+      </c>
+      <c r="D65" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="15"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="15"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="C69" s="13">
+        <v>250</v>
+      </c>
+      <c r="D69" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
+        <v>697</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="C71" s="13">
+        <v>250</v>
+      </c>
+      <c r="D71" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="15"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>699</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="C73" s="13">
+        <v>250</v>
+      </c>
+      <c r="D73" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="15"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="15"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="13">
+        <v>250</v>
+      </c>
+      <c r="D77" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="15"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19"/>
+    </row>
+    <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C85" s="7">
+        <v>250</v>
+      </c>
+      <c r="D85" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="15"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" s="13">
+        <v>250</v>
+      </c>
+      <c r="D87" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
+        <v>724</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="C89" s="13">
+        <v>250</v>
+      </c>
+      <c r="D89" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="B91" s="12"/>
+      <c r="C91" s="13">
+        <v>250</v>
+      </c>
+      <c r="D91" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="14" t="s">
+        <v>729</v>
+      </c>
+      <c r="B93" s="12"/>
+      <c r="C93" s="13">
+        <v>250</v>
+      </c>
+      <c r="D93" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="B95" s="12"/>
+      <c r="C95" s="13">
+        <v>250</v>
+      </c>
+      <c r="D95" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="B97" s="12"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="15"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
+        <v>734</v>
+      </c>
+      <c r="B99" s="12"/>
+      <c r="C99" s="13">
+        <v>250</v>
+      </c>
+      <c r="D99" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="11"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="15"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+    </row>
+    <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16"/>
+    </row>
+    <row r="104" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="B104" s="18"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18"/>
+      <c r="I104" s="19"/>
+    </row>
+    <row r="105" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C106" s="7">
+        <v>250</v>
+      </c>
+      <c r="D106" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="15"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="14" t="s">
+        <v>737</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C108" s="13">
+        <v>250</v>
+      </c>
+      <c r="D108" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="11"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="15"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="E109" s="10"/>
+      <c r="F109" s="10"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="11"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="B110" s="12"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="11"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="15"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="10"/>
+      <c r="D111" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="E111" s="10"/>
+      <c r="F111" s="10"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="s">
+        <v>740</v>
+      </c>
+      <c r="B112" s="12"/>
+      <c r="C112" s="13">
+        <v>250</v>
+      </c>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="15"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="10"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="11"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
+        <v>741</v>
+      </c>
+      <c r="B114" s="12"/>
+      <c r="C114" s="13">
+        <v>250</v>
+      </c>
+      <c r="D114" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11"/>
+      <c r="I114" s="11"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="15"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
+        <v>743</v>
+      </c>
+      <c r="B116" s="12"/>
+      <c r="C116" s="13">
+        <v>250</v>
+      </c>
+      <c r="D116" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="15"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="E117" s="10"/>
+      <c r="F117" s="10"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD8F5EC-C24E-492D-897C-0FB9BD38A5F7}">
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>746</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7">
+        <v>250</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13">
+        <v>250</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13">
+        <v>250</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>752</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13">
+        <v>250</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="C12" s="13">
+        <v>250</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13">
+        <v>250</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>759</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>764</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13">
+        <v>250</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13">
+        <v>250</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13">
+        <v>250</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+    </row>
+    <row r="29" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7">
+        <v>250</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="C33" s="13">
+        <v>250</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13">
+        <v>250</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>764</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13">
+        <v>250</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+    </row>
+    <row r="44" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="17" t="s">
+        <v>771</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="19"/>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="20" t="s">
+        <v>754</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="7">
+        <v>250</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13">
+        <v>250</v>
+      </c>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13">
+        <v>250</v>
+      </c>
+      <c r="D50" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85925C9E-4B5B-4B50-A16D-F247EAB10B79}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7">
+        <v>250</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>778</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13">
+        <v>250</v>
+      </c>
+      <c r="D8" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13">
+        <v>250</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7">
+        <v>250</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>778</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13">
+        <v>250</v>
+      </c>
+      <c r="D19" s="13">
+        <v>1200</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/import/ANNEX.xlsx
+++ b/data/import/ANNEX.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FD652A-C4E7-49D7-8A37-4D47F8CD2A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D77A19-B00B-4EFA-8758-556553606312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAC" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="787">
   <si>
     <t>الاسم واللقب</t>
   </si>
@@ -2378,6 +2378,12 @@
   </si>
   <si>
     <t>3 ابتدائي رياضيات</t>
+  </si>
+  <si>
+    <t>مخلوفي محمد لؤي</t>
+  </si>
+  <si>
+    <t>BON 100(07/10/2026)</t>
   </si>
 </sst>
 </file>
@@ -2664,7 +2670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -2705,11 +2711,14 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
@@ -2726,21 +2735,11 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3091,28 +3090,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -3144,7 +3143,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -3163,7 +3162,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>24</v>
@@ -3178,7 +3177,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -3197,7 +3196,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>25</v>
@@ -3212,7 +3211,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -3231,7 +3230,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>26</v>
@@ -3246,7 +3245,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -3265,7 +3264,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>27</v>
@@ -3280,7 +3279,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -3299,7 +3298,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>28</v>
@@ -3314,7 +3313,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="12"/>
@@ -3331,7 +3330,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>29</v>
@@ -3363,28 +3362,28 @@
       <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -3416,7 +3415,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -3435,7 +3434,7 @@
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10" t="s">
         <v>36</v>
@@ -3450,7 +3449,7 @@
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -3467,7 +3466,7 @@
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="9"/>
       <c r="C24" s="10" t="s">
         <v>40</v>
@@ -3480,7 +3479,7 @@
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="21" t="s">
         <v>41</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -3499,7 +3498,7 @@
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10" t="s">
         <v>43</v>
@@ -3514,7 +3513,7 @@
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="21" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -3533,7 +3532,7 @@
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" ht="34.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>47</v>
@@ -3548,7 +3547,7 @@
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>49</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -3567,7 +3566,7 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10" t="s">
         <v>51</v>
@@ -3582,7 +3581,7 @@
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="21" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="6"/>
@@ -3597,7 +3596,7 @@
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10" t="s">
         <v>53</v>
@@ -3610,7 +3609,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="21" t="s">
         <v>54</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -3627,7 +3626,7 @@
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10" t="s">
@@ -3640,7 +3639,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B35" s="6"/>
@@ -3655,7 +3654,7 @@
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
@@ -3668,7 +3667,7 @@
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="21" t="s">
         <v>59</v>
       </c>
       <c r="B37" s="6"/>
@@ -3685,7 +3684,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10" t="s">
         <v>60</v>
@@ -3700,7 +3699,7 @@
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B39" s="6"/>
@@ -3717,7 +3716,7 @@
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>62</v>
@@ -3732,34 +3731,34 @@
       <c r="I40" s="11"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="20"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
@@ -3800,7 +3799,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="21" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -3822,7 +3821,7 @@
       <c r="L46" s="8"/>
     </row>
     <row r="47" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="9"/>
       <c r="C47" s="10" t="s">
         <v>66</v>
@@ -3840,7 +3839,7 @@
       <c r="L47" s="11"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="23" t="s">
         <v>67</v>
       </c>
       <c r="B48" s="12" t="s">
@@ -3862,7 +3861,7 @@
       <c r="L48" s="11"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="9"/>
       <c r="C49" s="10" t="s">
         <v>69</v>
@@ -3880,7 +3879,7 @@
       <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="23" t="s">
         <v>70</v>
       </c>
       <c r="B50" s="12" t="s">
@@ -3902,7 +3901,7 @@
       <c r="L50" s="11"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="9"/>
       <c r="C51" s="10" t="s">
         <v>72</v>
@@ -3920,7 +3919,7 @@
       <c r="L51" s="11"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="23" t="s">
         <v>73</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -3940,7 +3939,7 @@
       <c r="L52" s="11"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="9"/>
       <c r="C53" s="10" t="s">
         <v>75</v>
@@ -3956,7 +3955,7 @@
       <c r="L53" s="11"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="23" t="s">
         <v>76</v>
       </c>
       <c r="B54" s="12" t="s">
@@ -3978,7 +3977,7 @@
       <c r="L54" s="11"/>
     </row>
     <row r="55" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="9"/>
       <c r="C55" s="10" t="s">
         <v>78</v>
@@ -3996,7 +3995,7 @@
       <c r="L55" s="11"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="23" t="s">
         <v>79</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -4020,7 +4019,7 @@
       <c r="L56" s="11"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="9"/>
       <c r="C57" s="10" t="s">
         <v>81</v>
@@ -4040,7 +4039,7 @@
       <c r="L57" s="11"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B58" s="12" t="s">
@@ -4064,7 +4063,7 @@
       <c r="L58" s="11"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="10" t="s">
         <v>84</v>
@@ -4084,7 +4083,7 @@
       <c r="L59" s="11"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="23" t="s">
         <v>85</v>
       </c>
       <c r="B60" s="12"/>
@@ -4106,7 +4105,7 @@
       <c r="L60" s="11"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="10" t="s">
         <v>86</v>
@@ -4126,7 +4125,7 @@
       <c r="L61" s="11"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="23" t="s">
         <v>87</v>
       </c>
       <c r="B62" s="12"/>
@@ -4146,7 +4145,7 @@
       <c r="L62" s="11"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="9"/>
       <c r="C63" s="10" t="s">
         <v>88</v>
@@ -4164,7 +4163,7 @@
       <c r="L63" s="11"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="23" t="s">
         <v>89</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -4186,7 +4185,7 @@
       <c r="L64" s="11"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="9"/>
       <c r="C65" s="10" t="s">
         <v>91</v>
@@ -4204,7 +4203,7 @@
       <c r="L65" s="11"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="23" t="s">
         <v>92</v>
       </c>
       <c r="B66" s="12" t="s">
@@ -4230,7 +4229,7 @@
       <c r="L66" s="11"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="9"/>
       <c r="C67" s="10" t="s">
         <v>94</v>
@@ -4252,7 +4251,7 @@
       <c r="L67" s="11"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="23" t="s">
         <v>95</v>
       </c>
       <c r="B68" s="12"/>
@@ -4274,7 +4273,7 @@
       <c r="L68" s="11"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="9"/>
       <c r="C69" s="10" t="s">
         <v>96</v>
@@ -4294,7 +4293,7 @@
       <c r="L69" s="11"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="23" t="s">
         <v>97</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -4316,7 +4315,7 @@
       <c r="L70" s="11"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
         <v>99</v>
@@ -4334,7 +4333,7 @@
       <c r="L71" s="11"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="23" t="s">
         <v>100</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -4356,7 +4355,7 @@
       <c r="L72" s="11"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
         <v>102</v>
@@ -4374,7 +4373,7 @@
       <c r="L73" s="11"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="23" t="s">
         <v>103</v>
       </c>
       <c r="B74" s="12" t="s">
@@ -4396,7 +4395,7 @@
       <c r="L74" s="11"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="22"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10" t="s">
         <v>105</v>
@@ -4414,7 +4413,7 @@
       <c r="L75" s="11"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="23" t="s">
         <v>106</v>
       </c>
       <c r="B76" s="12" t="s">
@@ -4438,7 +4437,7 @@
       <c r="L76" s="11"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="22"/>
       <c r="B77" s="9"/>
       <c r="C77" s="10" t="s">
         <v>108</v>
@@ -4458,7 +4457,7 @@
       <c r="L77" s="11"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="23" t="s">
         <v>109</v>
       </c>
       <c r="B78" s="12" t="s">
@@ -4480,7 +4479,7 @@
       <c r="L78" s="11"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="22"/>
       <c r="B79" s="9"/>
       <c r="C79" s="10" t="s">
         <v>111</v>
@@ -4498,7 +4497,7 @@
       <c r="L79" s="11"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="23" t="s">
         <v>112</v>
       </c>
       <c r="B80" s="12" t="s">
@@ -4520,7 +4519,7 @@
       <c r="L80" s="11"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="9"/>
       <c r="C81" s="10" t="s">
         <v>114</v>
@@ -4538,7 +4537,7 @@
       <c r="L81" s="11"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="23" t="s">
         <v>115</v>
       </c>
       <c r="B82" s="12" t="s">
@@ -4560,7 +4559,7 @@
       <c r="L82" s="11"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="9"/>
       <c r="C83" s="10" t="s">
         <v>117</v>
@@ -4578,7 +4577,7 @@
       <c r="L83" s="11"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="23" t="s">
         <v>118</v>
       </c>
       <c r="B84" s="12" t="s">
@@ -4600,7 +4599,7 @@
       <c r="L84" s="11"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="9"/>
       <c r="C85" s="10" t="s">
         <v>120</v>
@@ -4618,7 +4617,7 @@
       <c r="L85" s="11"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="23" t="s">
         <v>121</v>
       </c>
       <c r="B86" s="12" t="s">
@@ -4640,7 +4639,7 @@
       <c r="L86" s="11"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="9"/>
       <c r="C87" s="10" t="s">
         <v>123</v>
@@ -4658,7 +4657,7 @@
       <c r="L87" s="11"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="23" t="s">
         <v>124</v>
       </c>
       <c r="B88" s="12" t="s">
@@ -4680,7 +4679,7 @@
       <c r="L88" s="11"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="9"/>
       <c r="C89" s="10" t="s">
         <v>126</v>
@@ -4698,28 +4697,28 @@
       <c r="L89" s="11"/>
     </row>
     <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="16"/>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
-      <c r="H92" s="16"/>
-      <c r="I92" s="16"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="17"/>
+      <c r="I92" s="17"/>
     </row>
     <row r="93" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="18"/>
-      <c r="I93" s="19"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="19"/>
+      <c r="I93" s="20"/>
     </row>
     <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
@@ -4751,7 +4750,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="21" t="s">
         <v>139</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -4768,7 +4767,7 @@
       <c r="I95" s="8"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="9"/>
       <c r="C96" s="10" t="s">
         <v>141</v>
@@ -4781,7 +4780,7 @@
       <c r="I96" s="11"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="23" t="s">
         <v>142</v>
       </c>
       <c r="B97" s="12" t="s">
@@ -4802,7 +4801,7 @@
       <c r="I97" s="11"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
+      <c r="A98" s="22"/>
       <c r="B98" s="9"/>
       <c r="C98" s="10" t="s">
         <v>144</v>
@@ -4819,7 +4818,7 @@
       <c r="I98" s="11"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B99" s="12" t="s">
@@ -4838,7 +4837,7 @@
       <c r="I99" s="11"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="9"/>
       <c r="C100" s="10" t="s">
         <v>149</v>
@@ -4853,7 +4852,7 @@
       <c r="I100" s="11"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="23" t="s">
         <v>150</v>
       </c>
       <c r="B101" s="12"/>
@@ -4868,7 +4867,7 @@
       <c r="I101" s="11"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="15"/>
+      <c r="A102" s="22"/>
       <c r="B102" s="9"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10" t="s">
@@ -4881,7 +4880,7 @@
       <c r="I102" s="11"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="23" t="s">
         <v>152</v>
       </c>
       <c r="B103" s="12" t="s">
@@ -4902,7 +4901,7 @@
       <c r="I103" s="11"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="15"/>
+      <c r="A104" s="22"/>
       <c r="B104" s="9"/>
       <c r="C104" s="10" t="s">
         <v>154</v>
@@ -4919,7 +4918,7 @@
       <c r="I104" s="11"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="14" t="s">
+      <c r="A105" s="23" t="s">
         <v>156</v>
       </c>
       <c r="B105" s="12" t="s">
@@ -4938,7 +4937,7 @@
       <c r="I105" s="11"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="15"/>
+      <c r="A106" s="22"/>
       <c r="B106" s="9"/>
       <c r="C106" s="10" t="s">
         <v>158</v>
@@ -4953,7 +4952,7 @@
       <c r="I106" s="11"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="23" t="s">
         <v>159</v>
       </c>
       <c r="B107" s="12"/>
@@ -4968,7 +4967,7 @@
       <c r="I107" s="11"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="15"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="9"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10" t="s">
@@ -4981,7 +4980,7 @@
       <c r="I108" s="11"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="23" t="s">
         <v>161</v>
       </c>
       <c r="B109" s="12" t="s">
@@ -5002,7 +5001,7 @@
       <c r="I109" s="11"/>
     </row>
     <row r="110" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="15"/>
+      <c r="A110" s="22"/>
       <c r="B110" s="9"/>
       <c r="C110" s="10"/>
       <c r="D110" s="10" t="s">
@@ -5019,7 +5018,7 @@
       <c r="I110" s="11"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="23" t="s">
         <v>164</v>
       </c>
       <c r="B111" s="12" t="s">
@@ -5038,7 +5037,7 @@
       <c r="I111" s="11"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="15"/>
+      <c r="A112" s="22"/>
       <c r="B112" s="9"/>
       <c r="C112" s="10" t="s">
         <v>166</v>
@@ -5053,7 +5052,7 @@
       <c r="I112" s="11"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="23" t="s">
         <v>167</v>
       </c>
       <c r="B113" s="12" t="s">
@@ -5072,7 +5071,7 @@
       <c r="I113" s="11"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="15"/>
+      <c r="A114" s="22"/>
       <c r="B114" s="9"/>
       <c r="C114" s="10" t="s">
         <v>169</v>
@@ -5087,7 +5086,7 @@
       <c r="I114" s="11"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="23" t="s">
         <v>170</v>
       </c>
       <c r="B115" s="12" t="s">
@@ -5106,7 +5105,7 @@
       <c r="I115" s="11"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="15"/>
+      <c r="A116" s="22"/>
       <c r="B116" s="9"/>
       <c r="C116" s="10" t="s">
         <v>173</v>
@@ -5121,7 +5120,7 @@
       <c r="I116" s="11"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="23" t="s">
         <v>175</v>
       </c>
       <c r="B117" s="12" t="s">
@@ -5140,7 +5139,7 @@
       <c r="I117" s="11"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="15"/>
+      <c r="A118" s="22"/>
       <c r="B118" s="9"/>
       <c r="C118" s="10" t="s">
         <v>177</v>
@@ -5155,7 +5154,7 @@
       <c r="I118" s="11"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="23" t="s">
         <v>178</v>
       </c>
       <c r="B119" s="12" t="s">
@@ -5174,7 +5173,7 @@
       <c r="I119" s="11"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="15"/>
+      <c r="A120" s="22"/>
       <c r="B120" s="9"/>
       <c r="C120" s="10" t="s">
         <v>180</v>
@@ -5189,7 +5188,7 @@
       <c r="I120" s="11"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="23" t="s">
         <v>181</v>
       </c>
       <c r="B121" s="12" t="s">
@@ -5208,7 +5207,7 @@
       <c r="I121" s="11"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="15"/>
+      <c r="A122" s="22"/>
       <c r="B122" s="9"/>
       <c r="C122" s="10" t="s">
         <v>183</v>
@@ -5223,34 +5222,34 @@
       <c r="I122" s="11"/>
     </row>
     <row r="125" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="16"/>
-      <c r="B125" s="16"/>
-      <c r="C125" s="16"/>
-      <c r="D125" s="16"/>
-      <c r="E125" s="16"/>
-      <c r="F125" s="16"/>
-      <c r="G125" s="16"/>
-      <c r="H125" s="16"/>
-      <c r="I125" s="16"/>
-      <c r="J125" s="16"/>
-      <c r="K125" s="16"/>
-      <c r="L125" s="16"/>
+      <c r="A125" s="17"/>
+      <c r="B125" s="17"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="17"/>
+      <c r="I125" s="17"/>
+      <c r="J125" s="17"/>
+      <c r="K125" s="17"/>
+      <c r="L125" s="17"/>
     </row>
     <row r="126" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B126" s="18"/>
-      <c r="C126" s="18"/>
-      <c r="D126" s="18"/>
-      <c r="E126" s="18"/>
-      <c r="F126" s="18"/>
-      <c r="G126" s="18"/>
-      <c r="H126" s="18"/>
-      <c r="I126" s="18"/>
-      <c r="J126" s="18"/>
-      <c r="K126" s="18"/>
-      <c r="L126" s="19"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="19"/>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19"/>
+      <c r="K126" s="19"/>
+      <c r="L126" s="20"/>
     </row>
     <row r="127" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
@@ -5291,7 +5290,7 @@
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="20" t="s">
+      <c r="A128" s="21" t="s">
         <v>186</v>
       </c>
       <c r="B128" s="6" t="s">
@@ -5317,7 +5316,7 @@
       <c r="L128" s="8"/>
     </row>
     <row r="129" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="22"/>
       <c r="B129" s="9"/>
       <c r="C129" s="10" t="s">
         <v>188</v>
@@ -5339,7 +5338,7 @@
       <c r="L129" s="11"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="23" t="s">
         <v>189</v>
       </c>
       <c r="B130" s="12" t="s">
@@ -5365,7 +5364,7 @@
       <c r="L130" s="11"/>
     </row>
     <row r="131" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="22"/>
       <c r="B131" s="9"/>
       <c r="C131" s="10" t="s">
         <v>191</v>
@@ -5387,7 +5386,7 @@
       <c r="L131" s="11"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="23" t="s">
         <v>192</v>
       </c>
       <c r="B132" s="12" t="s">
@@ -5413,7 +5412,7 @@
       <c r="L132" s="11"/>
     </row>
     <row r="133" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="22"/>
       <c r="B133" s="9"/>
       <c r="C133" s="10" t="s">
         <v>194</v>
@@ -5435,7 +5434,7 @@
       <c r="L133" s="11"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="23" t="s">
         <v>195</v>
       </c>
       <c r="B134" s="12" t="s">
@@ -5461,7 +5460,7 @@
       <c r="L134" s="11"/>
     </row>
     <row r="135" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="22"/>
       <c r="B135" s="9"/>
       <c r="C135" s="10" t="s">
         <v>197</v>
@@ -5483,7 +5482,7 @@
       <c r="L135" s="11"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="23" t="s">
         <v>231</v>
       </c>
       <c r="B136" s="12" t="s">
@@ -5509,7 +5508,7 @@
       <c r="L136" s="11"/>
     </row>
     <row r="137" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="22"/>
       <c r="B137" s="9"/>
       <c r="C137" s="10" t="s">
         <v>199</v>
@@ -5531,7 +5530,7 @@
       <c r="L137" s="11"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="23" t="s">
         <v>200</v>
       </c>
       <c r="B138" s="12" t="s">
@@ -5557,7 +5556,7 @@
       <c r="L138" s="11"/>
     </row>
     <row r="139" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="22"/>
       <c r="B139" s="9"/>
       <c r="C139" s="10" t="s">
         <v>202</v>
@@ -5579,7 +5578,7 @@
       <c r="L139" s="11"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="23" t="s">
         <v>203</v>
       </c>
       <c r="B140" s="12" t="s">
@@ -5605,7 +5604,7 @@
       <c r="L140" s="11"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="22"/>
       <c r="B141" s="9"/>
       <c r="C141" s="10" t="s">
         <v>205</v>
@@ -5627,7 +5626,7 @@
       <c r="L141" s="11"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="23" t="s">
         <v>206</v>
       </c>
       <c r="B142" s="12" t="s">
@@ -5653,7 +5652,7 @@
       <c r="L142" s="11"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="9"/>
       <c r="C143" s="10" t="s">
         <v>208</v>
@@ -5675,7 +5674,7 @@
       <c r="L143" s="11"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="23" t="s">
         <v>209</v>
       </c>
       <c r="B144" s="12"/>
@@ -5695,7 +5694,7 @@
       <c r="L144" s="11"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="22"/>
       <c r="B145" s="9"/>
       <c r="C145" s="10"/>
       <c r="D145" s="10" t="s">
@@ -5713,7 +5712,7 @@
       <c r="L145" s="11"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="14" t="s">
+      <c r="A146" s="23" t="s">
         <v>230</v>
       </c>
       <c r="B146" s="12"/>
@@ -5735,7 +5734,7 @@
       <c r="L146" s="11"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="22"/>
       <c r="B147" s="9"/>
       <c r="C147" s="10"/>
       <c r="D147" s="10" t="s">
@@ -5755,28 +5754,28 @@
       <c r="L147" s="11"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="16"/>
-      <c r="B150" s="16"/>
-      <c r="C150" s="16"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-      <c r="H150" s="16"/>
-      <c r="I150" s="16"/>
+      <c r="A150" s="17"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="17"/>
+      <c r="H150" s="17"/>
+      <c r="I150" s="17"/>
     </row>
     <row r="151" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="17" t="s">
+      <c r="A151" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="18"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="18"/>
-      <c r="H151" s="18"/>
-      <c r="I151" s="19"/>
+      <c r="B151" s="19"/>
+      <c r="C151" s="19"/>
+      <c r="D151" s="19"/>
+      <c r="E151" s="19"/>
+      <c r="F151" s="19"/>
+      <c r="G151" s="19"/>
+      <c r="H151" s="19"/>
+      <c r="I151" s="20"/>
     </row>
     <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
@@ -5808,7 +5807,7 @@
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="20" t="s">
+      <c r="A153" s="21" t="s">
         <v>235</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -5827,7 +5826,7 @@
       <c r="I153" s="8"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="15"/>
+      <c r="A154" s="22"/>
       <c r="B154" s="9"/>
       <c r="C154" s="10" t="s">
         <v>237</v>
@@ -5842,7 +5841,7 @@
       <c r="I154" s="11"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="14" t="s">
+      <c r="A155" s="23" t="s">
         <v>238</v>
       </c>
       <c r="B155" s="12" t="s">
@@ -5861,7 +5860,7 @@
       <c r="I155" s="11"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15"/>
+      <c r="A156" s="22"/>
       <c r="B156" s="9"/>
       <c r="C156" s="10" t="s">
         <v>240</v>
@@ -5876,7 +5875,7 @@
       <c r="I156" s="11"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="20" t="s">
+      <c r="A157" s="21" t="s">
         <v>241</v>
       </c>
       <c r="B157" s="6" t="s">
@@ -5895,7 +5894,7 @@
       <c r="I157" s="8"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15"/>
+      <c r="A158" s="22"/>
       <c r="B158" s="9"/>
       <c r="C158" s="10" t="s">
         <v>243</v>
@@ -5910,7 +5909,7 @@
       <c r="I158" s="11"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="20" t="s">
+      <c r="A159" s="21" t="s">
         <v>244</v>
       </c>
       <c r="B159" s="6" t="s">
@@ -5929,7 +5928,7 @@
       <c r="I159" s="8"/>
     </row>
     <row r="160" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15"/>
+      <c r="A160" s="22"/>
       <c r="B160" s="9"/>
       <c r="C160" s="10" t="s">
         <v>246</v>
@@ -5944,7 +5943,7 @@
       <c r="I160" s="11"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="20" t="s">
+      <c r="A161" s="21" t="s">
         <v>247</v>
       </c>
       <c r="B161" s="6" t="s">
@@ -5963,7 +5962,7 @@
       <c r="I161" s="8"/>
     </row>
     <row r="162" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15"/>
+      <c r="A162" s="22"/>
       <c r="B162" s="9"/>
       <c r="C162" s="10" t="s">
         <v>249</v>
@@ -5978,7 +5977,7 @@
       <c r="I162" s="11"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="20" t="s">
+      <c r="A163" s="21" t="s">
         <v>250</v>
       </c>
       <c r="B163" s="6" t="s">
@@ -5997,7 +5996,7 @@
       <c r="I163" s="8"/>
     </row>
     <row r="164" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15"/>
+      <c r="A164" s="22"/>
       <c r="B164" s="9"/>
       <c r="C164" s="10" t="s">
         <v>252</v>
@@ -6012,7 +6011,7 @@
       <c r="I164" s="11"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="20" t="s">
+      <c r="A165" s="21" t="s">
         <v>253</v>
       </c>
       <c r="B165" s="6" t="s">
@@ -6031,7 +6030,7 @@
       <c r="I165" s="8"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="15"/>
+      <c r="A166" s="22"/>
       <c r="B166" s="9"/>
       <c r="C166" s="10" t="s">
         <v>255</v>
@@ -6046,28 +6045,28 @@
       <c r="I166" s="11"/>
     </row>
     <row r="169" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="16"/>
-      <c r="B169" s="16"/>
-      <c r="C169" s="16"/>
-      <c r="D169" s="16"/>
-      <c r="E169" s="16"/>
-      <c r="F169" s="16"/>
-      <c r="G169" s="16"/>
-      <c r="H169" s="16"/>
-      <c r="I169" s="16"/>
+      <c r="A169" s="17"/>
+      <c r="B169" s="17"/>
+      <c r="C169" s="17"/>
+      <c r="D169" s="17"/>
+      <c r="E169" s="17"/>
+      <c r="F169" s="17"/>
+      <c r="G169" s="17"/>
+      <c r="H169" s="17"/>
+      <c r="I169" s="17"/>
     </row>
     <row r="170" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="17" t="s">
+      <c r="A170" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B170" s="18"/>
-      <c r="C170" s="18"/>
-      <c r="D170" s="18"/>
-      <c r="E170" s="18"/>
-      <c r="F170" s="18"/>
-      <c r="G170" s="18"/>
-      <c r="H170" s="18"/>
-      <c r="I170" s="19"/>
+      <c r="B170" s="19"/>
+      <c r="C170" s="19"/>
+      <c r="D170" s="19"/>
+      <c r="E170" s="19"/>
+      <c r="F170" s="19"/>
+      <c r="G170" s="19"/>
+      <c r="H170" s="19"/>
+      <c r="I170" s="20"/>
     </row>
     <row r="171" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
@@ -6099,7 +6098,7 @@
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="20" t="s">
+      <c r="A172" s="21" t="s">
         <v>257</v>
       </c>
       <c r="B172" s="6" t="s">
@@ -6118,7 +6117,7 @@
       <c r="I172" s="8"/>
     </row>
     <row r="173" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="22"/>
       <c r="B173" s="9"/>
       <c r="C173" s="10" t="s">
         <v>259</v>
@@ -6133,7 +6132,7 @@
       <c r="I173" s="11"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="23" t="s">
         <v>260</v>
       </c>
       <c r="B174" s="12" t="s">
@@ -6152,7 +6151,7 @@
       <c r="I174" s="11"/>
     </row>
     <row r="175" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="22"/>
       <c r="B175" s="9"/>
       <c r="C175" s="10" t="s">
         <v>262</v>
@@ -6167,7 +6166,7 @@
       <c r="I175" s="11"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="14" t="s">
+      <c r="A176" s="23" t="s">
         <v>264</v>
       </c>
       <c r="B176" s="12" t="s">
@@ -6186,7 +6185,7 @@
       <c r="I176" s="11"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="22"/>
       <c r="B177" s="9"/>
       <c r="C177" s="10" t="s">
         <v>266</v>
@@ -6201,7 +6200,7 @@
       <c r="I177" s="11"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="14" t="s">
+      <c r="A178" s="23" t="s">
         <v>267</v>
       </c>
       <c r="B178" s="12" t="s">
@@ -6218,7 +6217,7 @@
       <c r="I178" s="11"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="22"/>
       <c r="B179" s="9"/>
       <c r="C179" s="10"/>
       <c r="D179" s="10" t="s">
@@ -6231,7 +6230,7 @@
       <c r="I179" s="11"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="14" t="s">
+      <c r="A180" s="23" t="s">
         <v>270</v>
       </c>
       <c r="B180" s="12" t="s">
@@ -6250,7 +6249,7 @@
       <c r="I180" s="11"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="22"/>
       <c r="B181" s="9"/>
       <c r="C181" s="10" t="s">
         <v>272</v>
@@ -6265,7 +6264,7 @@
       <c r="I181" s="11"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="14" t="s">
+      <c r="A182" s="23" t="s">
         <v>273</v>
       </c>
       <c r="B182" s="12" t="s">
@@ -6282,7 +6281,7 @@
       <c r="I182" s="11"/>
     </row>
     <row r="183" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="22"/>
       <c r="B183" s="9"/>
       <c r="C183" s="10"/>
       <c r="D183" s="10" t="s">
@@ -6295,7 +6294,7 @@
       <c r="I183" s="11"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="14" t="s">
+      <c r="A184" s="23" t="s">
         <v>277</v>
       </c>
       <c r="B184" s="12"/>
@@ -6310,7 +6309,7 @@
       <c r="I184" s="11"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="22"/>
       <c r="B185" s="9"/>
       <c r="C185" s="10"/>
       <c r="D185" s="10" t="s">
@@ -6323,7 +6322,7 @@
       <c r="I185" s="11"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="14" t="s">
+      <c r="A186" s="23" t="s">
         <v>279</v>
       </c>
       <c r="B186" s="12" t="s">
@@ -6342,7 +6341,7 @@
       <c r="I186" s="11"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="22"/>
       <c r="B187" s="9"/>
       <c r="C187" s="10" t="s">
         <v>281</v>
@@ -6357,7 +6356,7 @@
       <c r="I187" s="11"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="14" t="s">
+      <c r="A188" s="23" t="s">
         <v>282</v>
       </c>
       <c r="B188" s="12" t="s">
@@ -6376,7 +6375,7 @@
       <c r="I188" s="11"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="22"/>
       <c r="B189" s="9"/>
       <c r="C189" s="10" t="s">
         <v>284</v>
@@ -6391,28 +6390,28 @@
       <c r="I189" s="11"/>
     </row>
     <row r="192" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="16"/>
-      <c r="B192" s="16"/>
-      <c r="C192" s="16"/>
-      <c r="D192" s="16"/>
-      <c r="E192" s="16"/>
-      <c r="F192" s="16"/>
-      <c r="G192" s="16"/>
-      <c r="H192" s="16"/>
-      <c r="I192" s="16"/>
+      <c r="A192" s="17"/>
+      <c r="B192" s="17"/>
+      <c r="C192" s="17"/>
+      <c r="D192" s="17"/>
+      <c r="E192" s="17"/>
+      <c r="F192" s="17"/>
+      <c r="G192" s="17"/>
+      <c r="H192" s="17"/>
+      <c r="I192" s="17"/>
     </row>
     <row r="193" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="17" t="s">
+      <c r="A193" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="B193" s="18"/>
-      <c r="C193" s="18"/>
-      <c r="D193" s="18"/>
-      <c r="E193" s="18"/>
-      <c r="F193" s="18"/>
-      <c r="G193" s="18"/>
-      <c r="H193" s="18"/>
-      <c r="I193" s="19"/>
+      <c r="B193" s="19"/>
+      <c r="C193" s="19"/>
+      <c r="D193" s="19"/>
+      <c r="E193" s="19"/>
+      <c r="F193" s="19"/>
+      <c r="G193" s="19"/>
+      <c r="H193" s="19"/>
+      <c r="I193" s="20"/>
     </row>
     <row r="194" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
@@ -6444,7 +6443,7 @@
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="20" t="s">
+      <c r="A195" s="21" t="s">
         <v>286</v>
       </c>
       <c r="B195" s="6"/>
@@ -6459,7 +6458,7 @@
       <c r="I195" s="8"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="15"/>
+      <c r="A196" s="22"/>
       <c r="B196" s="9"/>
       <c r="C196" s="10"/>
       <c r="D196" s="10" t="s">
@@ -6472,7 +6471,7 @@
       <c r="I196" s="11"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="14" t="s">
+      <c r="A197" s="23" t="s">
         <v>288</v>
       </c>
       <c r="B197" s="12"/>
@@ -6487,7 +6486,7 @@
       <c r="I197" s="11"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="15"/>
+      <c r="A198" s="22"/>
       <c r="B198" s="9"/>
       <c r="C198" s="10"/>
       <c r="D198" s="10" t="s">
@@ -6500,7 +6499,7 @@
       <c r="I198" s="11"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="23" t="s">
         <v>290</v>
       </c>
       <c r="B199" s="12"/>
@@ -6515,7 +6514,7 @@
       <c r="I199" s="11"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="15"/>
+      <c r="A200" s="22"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10"/>
       <c r="D200" s="10" t="s">
@@ -6528,7 +6527,7 @@
       <c r="I200" s="11"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="14" t="s">
+      <c r="A201" s="23" t="s">
         <v>292</v>
       </c>
       <c r="B201" s="12" t="s">
@@ -6547,7 +6546,7 @@
       <c r="I201" s="11"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="15"/>
+      <c r="A202" s="22"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
         <v>294</v>
@@ -6562,34 +6561,34 @@
       <c r="I202" s="11"/>
     </row>
     <row r="205" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="16"/>
-      <c r="B205" s="16"/>
-      <c r="C205" s="16"/>
-      <c r="D205" s="16"/>
-      <c r="E205" s="16"/>
-      <c r="F205" s="16"/>
-      <c r="G205" s="16"/>
-      <c r="H205" s="16"/>
-      <c r="I205" s="16"/>
-      <c r="J205" s="16"/>
-      <c r="K205" s="16"/>
-      <c r="L205" s="16"/>
+      <c r="A205" s="17"/>
+      <c r="B205" s="17"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
+      <c r="F205" s="17"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="17"/>
+      <c r="I205" s="17"/>
+      <c r="J205" s="17"/>
+      <c r="K205" s="17"/>
+      <c r="L205" s="17"/>
     </row>
     <row r="206" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="17" t="s">
+      <c r="A206" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B206" s="18"/>
-      <c r="C206" s="18"/>
-      <c r="D206" s="18"/>
-      <c r="E206" s="18"/>
-      <c r="F206" s="18"/>
-      <c r="G206" s="18"/>
-      <c r="H206" s="18"/>
-      <c r="I206" s="18"/>
-      <c r="J206" s="18"/>
-      <c r="K206" s="18"/>
-      <c r="L206" s="19"/>
+      <c r="B206" s="19"/>
+      <c r="C206" s="19"/>
+      <c r="D206" s="19"/>
+      <c r="E206" s="19"/>
+      <c r="F206" s="19"/>
+      <c r="G206" s="19"/>
+      <c r="H206" s="19"/>
+      <c r="I206" s="19"/>
+      <c r="J206" s="19"/>
+      <c r="K206" s="19"/>
+      <c r="L206" s="20"/>
     </row>
     <row r="207" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
@@ -6630,7 +6629,7 @@
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="20" t="s">
+      <c r="A208" s="21" t="s">
         <v>296</v>
       </c>
       <c r="B208" s="6"/>
@@ -6648,7 +6647,7 @@
       <c r="L208" s="8"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="15"/>
+      <c r="A209" s="22"/>
       <c r="B209" s="9"/>
       <c r="C209" s="10"/>
       <c r="D209" s="10" t="s">
@@ -6664,7 +6663,7 @@
       <c r="L209" s="11"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="14" t="s">
+      <c r="A210" s="23" t="s">
         <v>297</v>
       </c>
       <c r="B210" s="12" t="s">
@@ -6686,7 +6685,7 @@
       <c r="L210" s="11"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="15"/>
+      <c r="A211" s="22"/>
       <c r="B211" s="9"/>
       <c r="C211" s="10" t="s">
         <v>299</v>
@@ -6704,7 +6703,7 @@
       <c r="L211" s="11"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A212" s="14" t="s">
+      <c r="A212" s="23" t="s">
         <v>300</v>
       </c>
       <c r="B212" s="12" t="s">
@@ -6726,7 +6725,7 @@
       <c r="L212" s="11"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="15"/>
+      <c r="A213" s="22"/>
       <c r="B213" s="9"/>
       <c r="C213" s="10" t="s">
         <v>302</v>
@@ -6744,7 +6743,7 @@
       <c r="L213" s="11"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="14" t="s">
+      <c r="A214" s="23" t="s">
         <v>303</v>
       </c>
       <c r="B214" s="12"/>
@@ -6764,7 +6763,7 @@
       <c r="L214" s="11"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A215" s="15"/>
+      <c r="A215" s="22"/>
       <c r="B215" s="9"/>
       <c r="C215" s="10" t="s">
         <v>304</v>
@@ -6782,7 +6781,7 @@
       <c r="L215" s="11"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A216" s="14" t="s">
+      <c r="A216" s="23" t="s">
         <v>313</v>
       </c>
       <c r="B216" s="12"/>
@@ -6804,7 +6803,7 @@
       <c r="L216" s="11"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A217" s="15"/>
+      <c r="A217" s="22"/>
       <c r="B217" s="9"/>
       <c r="C217" s="10" t="s">
         <v>305</v>
@@ -6824,7 +6823,7 @@
       <c r="L217" s="11"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A218" s="14" t="s">
+      <c r="A218" s="23" t="s">
         <v>306</v>
       </c>
       <c r="B218" s="12"/>
@@ -6842,7 +6841,7 @@
       <c r="L218" s="11"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A219" s="15"/>
+      <c r="A219" s="22"/>
       <c r="B219" s="9"/>
       <c r="C219" s="10"/>
       <c r="D219" s="10" t="s">
@@ -6858,7 +6857,7 @@
       <c r="L219" s="11"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A220" s="14" t="s">
+      <c r="A220" s="23" t="s">
         <v>97</v>
       </c>
       <c r="B220" s="12"/>
@@ -6876,7 +6875,7 @@
       <c r="L220" s="11"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A221" s="15"/>
+      <c r="A221" s="22"/>
       <c r="B221" s="9"/>
       <c r="C221" s="10"/>
       <c r="D221" s="10" t="s">
@@ -6892,7 +6891,7 @@
       <c r="L221" s="11"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A222" s="14" t="s">
+      <c r="A222" s="23" t="s">
         <v>312</v>
       </c>
       <c r="B222" s="12"/>
@@ -6910,7 +6909,7 @@
       <c r="L222" s="11"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" s="15"/>
+      <c r="A223" s="22"/>
       <c r="B223" s="9"/>
       <c r="C223" s="10" t="s">
         <v>305</v>
@@ -6927,45 +6926,51 @@
     </row>
   </sheetData>
   <mergeCells count="108">
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A205:L205"/>
-    <mergeCell ref="A206:L206"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A192:I192"/>
-    <mergeCell ref="A193:I193"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:I169"/>
-    <mergeCell ref="A170:I170"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A150:I150"/>
-    <mergeCell ref="A151:I151"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="A126:L126"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="A134:A135"/>
     <mergeCell ref="A136:A137"/>
@@ -6990,51 +6995,45 @@
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A93:I93"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="A126:L126"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A150:I150"/>
+    <mergeCell ref="A151:I151"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:I169"/>
+    <mergeCell ref="A170:I170"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A192:I192"/>
+    <mergeCell ref="A193:I193"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A205:L205"/>
+    <mergeCell ref="A206:L206"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -7053,30 +7052,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -7106,7 +7105,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>314</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -7125,7 +7124,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>316</v>
@@ -7140,7 +7139,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="12"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -7151,7 +7150,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -7174,7 +7173,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L238"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -7184,34 +7183,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -7241,12 +7240,12 @@
       <c r="I3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>319</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -7263,12 +7262,10 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>321</v>
@@ -7281,12 +7278,10 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>322</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -7303,12 +7298,10 @@
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>324</v>
@@ -7321,12 +7314,10 @@
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>326</v>
       </c>
       <c r="B8" s="12"/>
@@ -7341,7 +7332,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>327</v>
@@ -7354,7 +7345,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>328</v>
       </c>
       <c r="B10" s="12"/>
@@ -7371,7 +7362,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>329</v>
@@ -7386,7 +7377,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>330</v>
       </c>
       <c r="B12" s="12"/>
@@ -7401,7 +7392,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -7414,7 +7405,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>332</v>
       </c>
       <c r="B14" s="12"/>
@@ -7431,7 +7422,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>333</v>
@@ -7446,7 +7437,7 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="23" t="s">
         <v>335</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -7465,7 +7456,7 @@
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10" t="s">
         <v>337</v>
@@ -7480,7 +7471,7 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="23" t="s">
         <v>338</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -7499,7 +7490,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10" t="s">
         <v>340</v>
@@ -7514,7 +7505,7 @@
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="23" t="s">
         <v>341</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -7533,7 +7524,7 @@
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10" t="s">
         <v>343</v>
@@ -7548,7 +7539,7 @@
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="23" t="s">
         <v>345</v>
       </c>
       <c r="B22" s="12"/>
@@ -7565,7 +7556,7 @@
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10" t="s">
         <v>346</v>
@@ -7580,28 +7571,28 @@
       <c r="I23" s="11"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -7633,7 +7624,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>348</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -7652,7 +7643,7 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10" t="s">
         <v>350</v>
@@ -7667,7 +7658,7 @@
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="23" t="s">
         <v>352</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -7686,7 +7677,7 @@
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10" t="s">
         <v>354</v>
@@ -7701,7 +7692,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="23" t="s">
         <v>389</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -7720,7 +7711,7 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10" t="s">
         <v>357</v>
@@ -7735,7 +7726,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="23" t="s">
         <v>359</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -7754,7 +7745,7 @@
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9"/>
       <c r="C36" s="10" t="s">
         <v>361</v>
@@ -7769,7 +7760,7 @@
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="23" t="s">
         <v>363</v>
       </c>
       <c r="B37" s="12" t="s">
@@ -7786,7 +7777,7 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10" t="s">
         <v>365</v>
@@ -7799,7 +7790,7 @@
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="23" t="s">
         <v>366</v>
       </c>
       <c r="B39" s="12" t="s">
@@ -7818,7 +7809,7 @@
       <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>365</v>
@@ -7833,7 +7824,7 @@
       <c r="I40" s="11"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="23" t="s">
         <v>368</v>
       </c>
       <c r="B41" s="12"/>
@@ -7848,7 +7839,7 @@
       <c r="I41" s="11"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="9"/>
       <c r="C42" s="10" t="s">
         <v>369</v>
@@ -7863,7 +7854,7 @@
       <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="23" t="s">
         <v>370</v>
       </c>
       <c r="B43" s="12" t="s">
@@ -7882,7 +7873,7 @@
       <c r="I43" s="11"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="9"/>
       <c r="C44" s="10" t="s">
         <v>372</v>
@@ -7897,7 +7888,7 @@
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="23" t="s">
         <v>373</v>
       </c>
       <c r="B45" s="12"/>
@@ -7914,7 +7905,7 @@
       <c r="I45" s="11"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="9"/>
       <c r="C46" s="10" t="s">
         <v>374</v>
@@ -7929,7 +7920,7 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="23" t="s">
         <v>375</v>
       </c>
       <c r="B47" s="12" t="s">
@@ -7948,7 +7939,7 @@
       <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="9"/>
       <c r="C48" s="10" t="s">
         <v>377</v>
@@ -7963,7 +7954,7 @@
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="23" t="s">
         <v>378</v>
       </c>
       <c r="B49" s="12" t="s">
@@ -7982,7 +7973,7 @@
       <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="9"/>
       <c r="C50" s="10" t="s">
         <v>380</v>
@@ -7997,7 +7988,7 @@
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="23" t="s">
         <v>382</v>
       </c>
       <c r="B51" s="12"/>
@@ -8014,7 +8005,7 @@
       <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="9"/>
       <c r="C52" s="10" t="s">
         <v>383</v>
@@ -8029,7 +8020,7 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="23" t="s">
         <v>385</v>
       </c>
       <c r="B53" s="12"/>
@@ -8046,7 +8037,7 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="9"/>
       <c r="C54" s="10" t="s">
         <v>386</v>
@@ -8061,7 +8052,7 @@
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="23" t="s">
         <v>387</v>
       </c>
       <c r="B55" s="12"/>
@@ -8078,7 +8069,7 @@
       <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="9"/>
       <c r="C56" s="10" t="s">
         <v>388</v>
@@ -8093,28 +8084,28 @@
       <c r="I56" s="11"/>
     </row>
     <row r="59" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
     </row>
     <row r="60" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="19"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="20"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -8146,7 +8137,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="21" t="s">
         <v>359</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -8165,7 +8156,7 @@
       <c r="I62" s="8"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="9"/>
       <c r="C63" s="10" t="s">
         <v>361</v>
@@ -8180,7 +8171,7 @@
       <c r="I63" s="11"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="23" t="s">
         <v>392</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -8199,7 +8190,7 @@
       <c r="I64" s="11"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="9"/>
       <c r="C65" s="10" t="s">
         <v>394</v>
@@ -8214,7 +8205,7 @@
       <c r="I65" s="11"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="23" t="s">
         <v>395</v>
       </c>
       <c r="B66" s="12" t="s">
@@ -8233,7 +8224,7 @@
       <c r="I66" s="11"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="9"/>
       <c r="C67" s="10" t="s">
         <v>397</v>
@@ -8248,7 +8239,7 @@
       <c r="I67" s="11"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="23" t="s">
         <v>399</v>
       </c>
       <c r="B68" s="12" t="s">
@@ -8267,7 +8258,7 @@
       <c r="I68" s="11"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="9"/>
       <c r="C69" s="10" t="s">
         <v>401</v>
@@ -8282,7 +8273,7 @@
       <c r="I69" s="11"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="23" t="s">
         <v>402</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -8301,7 +8292,7 @@
       <c r="I70" s="11"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
         <v>404</v>
@@ -8316,7 +8307,7 @@
       <c r="I71" s="11"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="23" t="s">
         <v>405</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -8335,7 +8326,7 @@
       <c r="I72" s="11"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
         <v>407</v>
@@ -8350,7 +8341,7 @@
       <c r="I73" s="11"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="23" t="s">
         <v>408</v>
       </c>
       <c r="B74" s="12"/>
@@ -8367,7 +8358,7 @@
       <c r="I74" s="11"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="22"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10" t="s">
         <v>409</v>
@@ -8382,7 +8373,7 @@
       <c r="I75" s="11"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="23" t="s">
         <v>335</v>
       </c>
       <c r="B76" s="12"/>
@@ -8399,7 +8390,7 @@
       <c r="I76" s="11"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="22"/>
       <c r="B77" s="9"/>
       <c r="C77" s="10" t="s">
         <v>410</v>
@@ -8414,7 +8405,7 @@
       <c r="I77" s="11"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="23" t="s">
         <v>387</v>
       </c>
       <c r="B78" s="12" t="s">
@@ -8433,7 +8424,7 @@
       <c r="I78" s="11"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="22"/>
       <c r="B79" s="9"/>
       <c r="C79" s="10" t="s">
         <v>412</v>
@@ -8448,7 +8439,7 @@
       <c r="I79" s="11"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="23" t="s">
         <v>373</v>
       </c>
       <c r="B80" s="12"/>
@@ -8465,7 +8456,7 @@
       <c r="I80" s="11"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="9"/>
       <c r="C81" s="10" t="s">
         <v>374</v>
@@ -8480,7 +8471,7 @@
       <c r="I81" s="11"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="23" t="s">
         <v>413</v>
       </c>
       <c r="B82" s="12" t="s">
@@ -8499,7 +8490,7 @@
       <c r="I82" s="11"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="9"/>
       <c r="C83" s="10" t="s">
         <v>415</v>
@@ -8514,7 +8505,7 @@
       <c r="I83" s="11"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="23" t="s">
         <v>416</v>
       </c>
       <c r="B84" s="12" t="s">
@@ -8533,7 +8524,7 @@
       <c r="I84" s="11"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="9"/>
       <c r="C85" s="10" t="s">
         <v>418</v>
@@ -8548,7 +8539,7 @@
       <c r="I85" s="11"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="23" t="s">
         <v>419</v>
       </c>
       <c r="B86" s="12"/>
@@ -8565,7 +8556,7 @@
       <c r="I86" s="11"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="9"/>
       <c r="C87" s="10" t="s">
         <v>420</v>
@@ -8580,7 +8571,7 @@
       <c r="I87" s="11"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="23" t="s">
         <v>421</v>
       </c>
       <c r="B88" s="12"/>
@@ -8597,7 +8588,7 @@
       <c r="I88" s="11"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="9"/>
       <c r="C89" s="10" t="s">
         <v>422</v>
@@ -8612,7 +8603,7 @@
       <c r="I89" s="11"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="23" t="s">
         <v>423</v>
       </c>
       <c r="B90" s="12"/>
@@ -8627,7 +8618,7 @@
       <c r="I90" s="11"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="22"/>
       <c r="B91" s="9"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10" t="s">
@@ -8640,7 +8631,7 @@
       <c r="I91" s="11"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="23" t="s">
         <v>425</v>
       </c>
       <c r="B92" s="12"/>
@@ -8657,7 +8648,7 @@
       <c r="I92" s="11"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="22"/>
       <c r="B93" s="9"/>
       <c r="C93" s="10" t="s">
         <v>426</v>
@@ -8672,7 +8663,7 @@
       <c r="I93" s="11"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="23" t="s">
         <v>427</v>
       </c>
       <c r="B94" s="12"/>
@@ -8689,7 +8680,7 @@
       <c r="I94" s="11"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="22"/>
       <c r="B95" s="9"/>
       <c r="C95" s="10" t="s">
         <v>428</v>
@@ -8704,7 +8695,7 @@
       <c r="I95" s="11"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="23" t="s">
         <v>429</v>
       </c>
       <c r="B96" s="12"/>
@@ -8721,7 +8712,7 @@
       <c r="I96" s="11"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="22"/>
       <c r="B97" s="9"/>
       <c r="C97" s="10" t="s">
         <v>430</v>
@@ -8736,7 +8727,7 @@
       <c r="I97" s="11"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="23" t="s">
         <v>431</v>
       </c>
       <c r="B98" s="12"/>
@@ -8753,7 +8744,7 @@
       <c r="I98" s="11"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="22"/>
       <c r="B99" s="9"/>
       <c r="C99" s="10" t="s">
         <v>432</v>
@@ -8768,7 +8759,7 @@
       <c r="I99" s="11"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="23" t="s">
         <v>433</v>
       </c>
       <c r="B100" s="12"/>
@@ -8785,7 +8776,7 @@
       <c r="I100" s="11"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="22"/>
       <c r="B101" s="9"/>
       <c r="C101" s="10" t="s">
         <v>434</v>
@@ -8800,28 +8791,28 @@
       <c r="I101" s="11"/>
     </row>
     <row r="104" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="16"/>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16"/>
-      <c r="E104" s="16"/>
-      <c r="F104" s="16"/>
-      <c r="G104" s="16"/>
-      <c r="H104" s="16"/>
-      <c r="I104" s="16"/>
+      <c r="A104" s="17"/>
+      <c r="B104" s="17"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="17"/>
+      <c r="G104" s="17"/>
+      <c r="H104" s="17"/>
+      <c r="I104" s="17"/>
     </row>
     <row r="105" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
-      <c r="H105" s="18"/>
-      <c r="I105" s="19"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="19"/>
+      <c r="E105" s="19"/>
+      <c r="F105" s="19"/>
+      <c r="G105" s="19"/>
+      <c r="H105" s="19"/>
+      <c r="I105" s="20"/>
     </row>
     <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
@@ -8853,7 +8844,7 @@
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="20" t="s">
+      <c r="A107" s="21" t="s">
         <v>436</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -8872,7 +8863,7 @@
       <c r="I107" s="8"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="15"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="9"/>
       <c r="C108" s="10" t="s">
         <v>438</v>
@@ -8887,7 +8878,7 @@
       <c r="I108" s="11"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="23" t="s">
         <v>439</v>
       </c>
       <c r="B109" s="12" t="s">
@@ -8906,7 +8897,7 @@
       <c r="I109" s="11"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="15"/>
+      <c r="A110" s="22"/>
       <c r="B110" s="9"/>
       <c r="C110" s="10" t="s">
         <v>441</v>
@@ -8921,7 +8912,7 @@
       <c r="I110" s="11"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="23" t="s">
         <v>443</v>
       </c>
       <c r="B111" s="12" t="s">
@@ -8940,7 +8931,7 @@
       <c r="I111" s="11"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="15"/>
+      <c r="A112" s="22"/>
       <c r="B112" s="9"/>
       <c r="C112" s="10" t="s">
         <v>442</v>
@@ -8955,7 +8946,7 @@
       <c r="I112" s="11"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="23" t="s">
         <v>445</v>
       </c>
       <c r="B113" s="12"/>
@@ -8970,7 +8961,7 @@
       <c r="I113" s="11"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="15"/>
+      <c r="A114" s="22"/>
       <c r="B114" s="9"/>
       <c r="C114" s="10"/>
       <c r="D114" s="10" t="s">
@@ -8983,28 +8974,28 @@
       <c r="I114" s="11"/>
     </row>
     <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="16"/>
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
-      <c r="D117" s="16"/>
-      <c r="E117" s="16"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="16"/>
-      <c r="H117" s="16"/>
-      <c r="I117" s="16"/>
+      <c r="A117" s="17"/>
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="17"/>
+      <c r="G117" s="17"/>
+      <c r="H117" s="17"/>
+      <c r="I117" s="17"/>
     </row>
     <row r="118" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="B118" s="18"/>
-      <c r="C118" s="18"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="18"/>
-      <c r="G118" s="18"/>
-      <c r="H118" s="18"/>
-      <c r="I118" s="19"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="20"/>
     </row>
     <row r="119" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
@@ -9036,7 +9027,7 @@
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="20" t="s">
+      <c r="A120" s="21" t="s">
         <v>359</v>
       </c>
       <c r="B120" s="6" t="s">
@@ -9055,7 +9046,7 @@
       <c r="I120" s="8"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="22"/>
       <c r="B121" s="9"/>
       <c r="C121" s="10" t="s">
         <v>361</v>
@@ -9070,7 +9061,7 @@
       <c r="I121" s="11"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="14" t="s">
+      <c r="A122" s="23" t="s">
         <v>448</v>
       </c>
       <c r="B122" s="12"/>
@@ -9087,7 +9078,7 @@
       <c r="I122" s="11"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="22"/>
       <c r="B123" s="9"/>
       <c r="C123" s="10" t="s">
         <v>449</v>
@@ -9102,7 +9093,7 @@
       <c r="I123" s="11"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="23" t="s">
         <v>387</v>
       </c>
       <c r="B124" s="12" t="s">
@@ -9121,7 +9112,7 @@
       <c r="I124" s="11"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="22"/>
       <c r="B125" s="9"/>
       <c r="C125" s="10" t="s">
         <v>412</v>
@@ -9136,7 +9127,7 @@
       <c r="I125" s="11"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="14" t="s">
+      <c r="A126" s="23" t="s">
         <v>366</v>
       </c>
       <c r="B126" s="12"/>
@@ -9153,7 +9144,7 @@
       <c r="I126" s="11"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="22"/>
       <c r="B127" s="9"/>
       <c r="C127" s="10" t="s">
         <v>409</v>
@@ -9168,7 +9159,7 @@
       <c r="I127" s="11"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="14" t="s">
+      <c r="A128" s="23" t="s">
         <v>450</v>
       </c>
       <c r="B128" s="12" t="s">
@@ -9187,7 +9178,7 @@
       <c r="I128" s="11"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="22"/>
       <c r="B129" s="9"/>
       <c r="C129" s="10" t="s">
         <v>452</v>
@@ -9202,7 +9193,7 @@
       <c r="I129" s="11"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="23" t="s">
         <v>453</v>
       </c>
       <c r="B130" s="12" t="s">
@@ -9223,7 +9214,7 @@
       <c r="I130" s="11"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="22"/>
       <c r="B131" s="9"/>
       <c r="C131" s="10" t="s">
         <v>455</v>
@@ -9240,7 +9231,7 @@
       <c r="I131" s="11"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="23" t="s">
         <v>335</v>
       </c>
       <c r="B132" s="12" t="s">
@@ -9259,7 +9250,7 @@
       <c r="I132" s="11"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="22"/>
       <c r="B133" s="9"/>
       <c r="C133" s="10" t="s">
         <v>410</v>
@@ -9274,7 +9265,7 @@
       <c r="I133" s="11"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="23" t="s">
         <v>456</v>
       </c>
       <c r="B134" s="12"/>
@@ -9291,7 +9282,7 @@
       <c r="I134" s="11"/>
     </row>
     <row r="135" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="22"/>
       <c r="B135" s="9"/>
       <c r="C135" s="10" t="s">
         <v>457</v>
@@ -9306,7 +9297,7 @@
       <c r="I135" s="11"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="23" t="s">
         <v>458</v>
       </c>
       <c r="B136" s="12" t="s">
@@ -9325,7 +9316,7 @@
       <c r="I136" s="11"/>
     </row>
     <row r="137" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="22"/>
       <c r="B137" s="9"/>
       <c r="C137" s="10" t="s">
         <v>460</v>
@@ -9340,7 +9331,7 @@
       <c r="I137" s="11"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="23" t="s">
         <v>402</v>
       </c>
       <c r="B138" s="12" t="s">
@@ -9359,7 +9350,7 @@
       <c r="I138" s="11"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="22"/>
       <c r="B139" s="9"/>
       <c r="C139" s="10" t="s">
         <v>462</v>
@@ -9374,7 +9365,7 @@
       <c r="I139" s="11"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="23" t="s">
         <v>464</v>
       </c>
       <c r="B140" s="12" t="s">
@@ -9393,7 +9384,7 @@
       <c r="I140" s="11"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="22"/>
       <c r="B141" s="9"/>
       <c r="C141" s="10" t="s">
         <v>466</v>
@@ -9408,7 +9399,7 @@
       <c r="I141" s="11"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="23" t="s">
         <v>467</v>
       </c>
       <c r="B142" s="12" t="s">
@@ -9427,7 +9418,7 @@
       <c r="I142" s="11"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="9"/>
       <c r="C143" s="10" t="s">
         <v>469</v>
@@ -9442,7 +9433,7 @@
       <c r="I143" s="11"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="23" t="s">
         <v>470</v>
       </c>
       <c r="B144" s="12" t="s">
@@ -9461,7 +9452,7 @@
       <c r="I144" s="11"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="22"/>
       <c r="B145" s="9"/>
       <c r="C145" s="10" t="s">
         <v>472</v>
@@ -9476,7 +9467,7 @@
       <c r="I145" s="11"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="14" t="s">
+      <c r="A146" s="23" t="s">
         <v>373</v>
       </c>
       <c r="B146" s="12"/>
@@ -9493,7 +9484,7 @@
       <c r="I146" s="11"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="22"/>
       <c r="B147" s="9"/>
       <c r="C147" s="10" t="s">
         <v>374</v>
@@ -9508,7 +9499,7 @@
       <c r="I147" s="11"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="14" t="s">
+      <c r="A148" s="23" t="s">
         <v>473</v>
       </c>
       <c r="B148" s="12" t="s">
@@ -9527,7 +9518,7 @@
       <c r="I148" s="11"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="22"/>
       <c r="B149" s="9"/>
       <c r="C149" s="10" t="s">
         <v>475</v>
@@ -9542,7 +9533,7 @@
       <c r="I149" s="11"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="14" t="s">
+      <c r="A150" s="23" t="s">
         <v>476</v>
       </c>
       <c r="B150" s="12" t="s">
@@ -9559,7 +9550,7 @@
       <c r="I150" s="11"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="22"/>
       <c r="B151" s="9"/>
       <c r="C151" s="10"/>
       <c r="D151" s="10" t="s">
@@ -9572,7 +9563,7 @@
       <c r="I151" s="11"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="23" t="s">
         <v>479</v>
       </c>
       <c r="B152" s="12" t="s">
@@ -9591,7 +9582,7 @@
       <c r="I152" s="11"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="22"/>
       <c r="B153" s="9"/>
       <c r="C153" s="10" t="s">
         <v>481</v>
@@ -9606,7 +9597,7 @@
       <c r="I153" s="11"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="s">
+      <c r="A154" s="23" t="s">
         <v>482</v>
       </c>
       <c r="B154" s="12" t="s">
@@ -9625,7 +9616,7 @@
       <c r="I154" s="11"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="22"/>
       <c r="B155" s="9"/>
       <c r="C155" s="10" t="s">
         <v>484</v>
@@ -9640,7 +9631,7 @@
       <c r="I155" s="11"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
+      <c r="A156" s="23" t="s">
         <v>485</v>
       </c>
       <c r="B156" s="12" t="s">
@@ -9659,7 +9650,7 @@
       <c r="I156" s="11"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="22"/>
       <c r="B157" s="9"/>
       <c r="C157" s="10" t="s">
         <v>487</v>
@@ -9674,7 +9665,7 @@
       <c r="I157" s="11"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="14" t="s">
+      <c r="A158" s="23" t="s">
         <v>488</v>
       </c>
       <c r="B158" s="12"/>
@@ -9691,7 +9682,7 @@
       <c r="I158" s="11"/>
     </row>
     <row r="159" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="22"/>
       <c r="B159" s="9"/>
       <c r="C159" s="10" t="s">
         <v>489</v>
@@ -9706,7 +9697,7 @@
       <c r="I159" s="11"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="14" t="s">
+      <c r="A160" s="23" t="s">
         <v>491</v>
       </c>
       <c r="B160" s="12" t="s">
@@ -9725,7 +9716,7 @@
       <c r="I160" s="11"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="22"/>
       <c r="B161" s="9"/>
       <c r="C161" s="10" t="s">
         <v>380</v>
@@ -9740,7 +9731,7 @@
       <c r="I161" s="11"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="23" t="s">
         <v>493</v>
       </c>
       <c r="B162" s="12" t="s">
@@ -9759,7 +9750,7 @@
       <c r="I162" s="11"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="22"/>
       <c r="B163" s="9"/>
       <c r="C163" s="10" t="s">
         <v>495</v>
@@ -9774,7 +9765,7 @@
       <c r="I163" s="11"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="14" t="s">
+      <c r="A164" s="23" t="s">
         <v>497</v>
       </c>
       <c r="B164" s="12"/>
@@ -9791,7 +9782,7 @@
       <c r="I164" s="11"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="22"/>
       <c r="B165" s="9"/>
       <c r="C165" s="10" t="s">
         <v>498</v>
@@ -9806,7 +9797,7 @@
       <c r="I165" s="11"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="14" t="s">
+      <c r="A166" s="23" t="s">
         <v>499</v>
       </c>
       <c r="B166" s="12"/>
@@ -9823,7 +9814,7 @@
       <c r="I166" s="11"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="22"/>
       <c r="B167" s="9"/>
       <c r="C167" s="10" t="s">
         <v>500</v>
@@ -9838,7 +9829,7 @@
       <c r="I167" s="11"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="14" t="s">
+      <c r="A168" s="23" t="s">
         <v>501</v>
       </c>
       <c r="B168" s="12"/>
@@ -9853,7 +9844,7 @@
       <c r="I168" s="11"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="22"/>
       <c r="B169" s="9"/>
       <c r="C169" s="10"/>
       <c r="D169" s="10" t="s">
@@ -9866,7 +9857,7 @@
       <c r="I169" s="11"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="14" t="s">
+      <c r="A170" s="23" t="s">
         <v>503</v>
       </c>
       <c r="B170" s="12"/>
@@ -9883,7 +9874,7 @@
       <c r="I170" s="11"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="22"/>
       <c r="B171" s="9"/>
       <c r="C171" s="10" t="s">
         <v>504</v>
@@ -9898,7 +9889,7 @@
       <c r="I171" s="11"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="14" t="s">
+      <c r="A172" s="23" t="s">
         <v>505</v>
       </c>
       <c r="B172" s="12"/>
@@ -9915,7 +9906,7 @@
       <c r="I172" s="11"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="22"/>
       <c r="B173" s="9"/>
       <c r="C173" s="10" t="s">
         <v>506</v>
@@ -9930,7 +9921,7 @@
       <c r="I173" s="11"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="23" t="s">
         <v>507</v>
       </c>
       <c r="B174" s="12"/>
@@ -9947,7 +9938,7 @@
       <c r="I174" s="11"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="22"/>
       <c r="B175" s="9"/>
       <c r="C175" s="10" t="s">
         <v>508</v>
@@ -9962,7 +9953,7 @@
       <c r="I175" s="11"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="14" t="s">
+      <c r="A176" s="23" t="s">
         <v>509</v>
       </c>
       <c r="B176" s="12"/>
@@ -9979,7 +9970,7 @@
       <c r="I176" s="11"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="22"/>
       <c r="B177" s="9"/>
       <c r="C177" s="10" t="s">
         <v>510</v>
@@ -9994,28 +9985,28 @@
       <c r="I177" s="11"/>
     </row>
     <row r="180" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="16"/>
-      <c r="B180" s="16"/>
-      <c r="C180" s="16"/>
-      <c r="D180" s="16"/>
-      <c r="E180" s="16"/>
-      <c r="F180" s="16"/>
-      <c r="G180" s="16"/>
-      <c r="H180" s="16"/>
-      <c r="I180" s="16"/>
+      <c r="A180" s="17"/>
+      <c r="B180" s="17"/>
+      <c r="C180" s="17"/>
+      <c r="D180" s="17"/>
+      <c r="E180" s="17"/>
+      <c r="F180" s="17"/>
+      <c r="G180" s="17"/>
+      <c r="H180" s="17"/>
+      <c r="I180" s="17"/>
     </row>
     <row r="181" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="17" t="s">
+      <c r="A181" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="B181" s="18"/>
-      <c r="C181" s="18"/>
-      <c r="D181" s="18"/>
-      <c r="E181" s="18"/>
-      <c r="F181" s="18"/>
-      <c r="G181" s="18"/>
-      <c r="H181" s="18"/>
-      <c r="I181" s="19"/>
+      <c r="B181" s="19"/>
+      <c r="C181" s="19"/>
+      <c r="D181" s="19"/>
+      <c r="E181" s="19"/>
+      <c r="F181" s="19"/>
+      <c r="G181" s="19"/>
+      <c r="H181" s="19"/>
+      <c r="I181" s="20"/>
     </row>
     <row r="182" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
@@ -10047,7 +10038,7 @@
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="20" t="s">
+      <c r="A183" s="21" t="s">
         <v>512</v>
       </c>
       <c r="B183" s="6"/>
@@ -10064,7 +10055,7 @@
       <c r="I183" s="8"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="15"/>
+      <c r="A184" s="22"/>
       <c r="B184" s="9"/>
       <c r="C184" s="10" t="s">
         <v>513</v>
@@ -10079,28 +10070,28 @@
       <c r="I184" s="11"/>
     </row>
     <row r="187" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="16"/>
-      <c r="B187" s="16"/>
-      <c r="C187" s="16"/>
-      <c r="D187" s="16"/>
-      <c r="E187" s="16"/>
-      <c r="F187" s="16"/>
-      <c r="G187" s="16"/>
-      <c r="H187" s="16"/>
-      <c r="I187" s="16"/>
+      <c r="A187" s="17"/>
+      <c r="B187" s="17"/>
+      <c r="C187" s="17"/>
+      <c r="D187" s="17"/>
+      <c r="E187" s="17"/>
+      <c r="F187" s="17"/>
+      <c r="G187" s="17"/>
+      <c r="H187" s="17"/>
+      <c r="I187" s="17"/>
     </row>
     <row r="188" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="17" t="s">
+      <c r="A188" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="B188" s="18"/>
-      <c r="C188" s="18"/>
-      <c r="D188" s="18"/>
-      <c r="E188" s="18"/>
-      <c r="F188" s="18"/>
-      <c r="G188" s="18"/>
-      <c r="H188" s="18"/>
-      <c r="I188" s="19"/>
+      <c r="B188" s="19"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="19"/>
+      <c r="E188" s="19"/>
+      <c r="F188" s="19"/>
+      <c r="G188" s="19"/>
+      <c r="H188" s="19"/>
+      <c r="I188" s="20"/>
     </row>
     <row r="189" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
@@ -10132,7 +10123,7 @@
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="20" t="s">
+      <c r="A190" s="21" t="s">
         <v>443</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -10151,7 +10142,7 @@
       <c r="I190" s="8"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="22"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
         <v>515</v>
@@ -10166,7 +10157,7 @@
       <c r="I191" s="11"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="14" t="s">
+      <c r="A192" s="23" t="s">
         <v>516</v>
       </c>
       <c r="B192" s="12"/>
@@ -10183,7 +10174,7 @@
       <c r="I192" s="11"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="15"/>
+      <c r="A193" s="22"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
         <v>517</v>
@@ -10197,117 +10188,115 @@
       <c r="H193" s="11"/>
       <c r="I193" s="11"/>
     </row>
-    <row r="196" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="16"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="16"/>
-      <c r="D196" s="16"/>
-      <c r="E196" s="16"/>
-      <c r="F196" s="16"/>
-      <c r="G196" s="16"/>
-      <c r="H196" s="16"/>
-      <c r="I196" s="16"/>
-    </row>
-    <row r="197" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="17" t="s">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="23" t="s">
+        <v>785</v>
+      </c>
+      <c r="B194" s="12"/>
+      <c r="C194" s="13">
+        <v>250</v>
+      </c>
+      <c r="D194" s="13"/>
+      <c r="E194" s="13"/>
+      <c r="F194" s="13"/>
+      <c r="G194" s="11"/>
+      <c r="H194" s="11"/>
+      <c r="I194" s="11"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="22"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="D195" s="10"/>
+      <c r="E195" s="10"/>
+      <c r="F195" s="10"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
+    </row>
+    <row r="198" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="17"/>
+      <c r="B198" s="17"/>
+      <c r="C198" s="17"/>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
+      <c r="F198" s="17"/>
+      <c r="G198" s="17"/>
+      <c r="H198" s="17"/>
+      <c r="I198" s="17"/>
+    </row>
+    <row r="199" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="18" t="s">
         <v>518</v>
       </c>
-      <c r="B197" s="18"/>
-      <c r="C197" s="18"/>
-      <c r="D197" s="18"/>
-      <c r="E197" s="18"/>
-      <c r="F197" s="18"/>
-      <c r="G197" s="18"/>
-      <c r="H197" s="18"/>
-      <c r="I197" s="19"/>
-    </row>
-    <row r="198" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="5" t="s">
+      <c r="B199" s="19"/>
+      <c r="C199" s="19"/>
+      <c r="D199" s="19"/>
+      <c r="E199" s="19"/>
+      <c r="F199" s="19"/>
+      <c r="G199" s="19"/>
+      <c r="H199" s="19"/>
+      <c r="I199" s="20"/>
+    </row>
+    <row r="200" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B200" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C200" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D198" s="5" t="s">
+      <c r="D200" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E198" s="5" t="s">
+      <c r="E200" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F200" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G200" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H198" s="5" t="s">
+      <c r="H200" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I198" s="5" t="s">
+      <c r="I200" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="20" t="s">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="21" t="s">
         <v>352</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B201" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C199" s="7">
-        <v>250</v>
-      </c>
-      <c r="D199" s="7">
+      <c r="C201" s="7">
+        <v>250</v>
+      </c>
+      <c r="D201" s="7">
         <v>1500</v>
       </c>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
-      <c r="G199" s="8"/>
-      <c r="H199" s="8"/>
-      <c r="I199" s="8"/>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="15"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="D200" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="E200" s="10"/>
-      <c r="F200" s="10"/>
-      <c r="G200" s="11"/>
-      <c r="H200" s="11"/>
-      <c r="I200" s="11"/>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C201" s="13">
-        <v>250</v>
-      </c>
-      <c r="D201" s="13"/>
-      <c r="E201" s="13"/>
-      <c r="F201" s="13"/>
-      <c r="G201" s="11"/>
-      <c r="H201" s="11"/>
-      <c r="I201" s="11"/>
-    </row>
-    <row r="202" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="15"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="8"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="22"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="D202" s="10"/>
+        <v>519</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>520</v>
+      </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="11"/>
@@ -10315,33 +10304,29 @@
       <c r="I202" s="11"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="C203" s="7">
-        <v>250</v>
-      </c>
-      <c r="D203" s="7">
-        <v>1500</v>
-      </c>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="8"/>
-      <c r="H203" s="8"/>
-      <c r="I203" s="8"/>
+      <c r="A203" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="C203" s="13">
+        <v>250</v>
+      </c>
+      <c r="D203" s="13"/>
+      <c r="E203" s="13"/>
+      <c r="F203" s="13"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="11"/>
+      <c r="I203" s="11"/>
     </row>
     <row r="204" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="15"/>
+      <c r="A204" s="22"/>
       <c r="B204" s="9"/>
       <c r="C204" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="D204" s="10" t="s">
-        <v>521</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="D204" s="10"/>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="11"/>
@@ -10349,11 +10334,11 @@
       <c r="I204" s="11"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="20" t="s">
-        <v>522</v>
+      <c r="A205" s="21" t="s">
+        <v>389</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>523</v>
+        <v>356</v>
       </c>
       <c r="C205" s="7">
         <v>250</v>
@@ -10368,13 +10353,13 @@
       <c r="I205" s="8"/>
     </row>
     <row r="206" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="15"/>
+      <c r="A206" s="22"/>
       <c r="B206" s="9"/>
       <c r="C206" s="10" t="s">
-        <v>524</v>
+        <v>357</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
@@ -10383,11 +10368,11 @@
       <c r="I206" s="11"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="20" t="s">
-        <v>526</v>
+      <c r="A207" s="21" t="s">
+        <v>522</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C207" s="7">
         <v>250</v>
@@ -10402,13 +10387,13 @@
       <c r="I207" s="8"/>
     </row>
     <row r="208" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="15"/>
+      <c r="A208" s="22"/>
       <c r="B208" s="9"/>
       <c r="C208" s="10" t="s">
-        <v>407</v>
+        <v>524</v>
       </c>
       <c r="D208" s="10" t="s">
-        <v>407</v>
+        <v>525</v>
       </c>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
@@ -10417,13 +10402,15 @@
       <c r="I208" s="11"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="20" t="s">
-        <v>366</v>
+      <c r="A209" s="21" t="s">
+        <v>526</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C209" s="7"/>
+        <v>527</v>
+      </c>
+      <c r="C209" s="7">
+        <v>250</v>
+      </c>
       <c r="D209" s="7">
         <v>1500</v>
       </c>
@@ -10434,11 +10421,13 @@
       <c r="I209" s="8"/>
     </row>
     <row r="210" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="15"/>
+      <c r="A210" s="22"/>
       <c r="B210" s="9"/>
-      <c r="C210" s="10"/>
+      <c r="C210" s="10" t="s">
+        <v>407</v>
+      </c>
       <c r="D210" s="10" t="s">
-        <v>528</v>
+        <v>407</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -10447,15 +10436,13 @@
       <c r="I210" s="11"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="20" t="s">
-        <v>529</v>
+      <c r="A211" s="21" t="s">
+        <v>366</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="C211" s="7">
-        <v>250</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C211" s="7"/>
       <c r="D211" s="7">
         <v>1500</v>
       </c>
@@ -10466,13 +10453,11 @@
       <c r="I211" s="8"/>
     </row>
     <row r="212" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="15"/>
+      <c r="A212" s="22"/>
       <c r="B212" s="9"/>
-      <c r="C212" s="10" t="s">
-        <v>531</v>
-      </c>
+      <c r="C212" s="10"/>
       <c r="D212" s="10" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
@@ -10481,10 +10466,12 @@
       <c r="I212" s="11"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B213" s="6"/>
+      <c r="A213" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>530</v>
+      </c>
       <c r="C213" s="7">
         <v>250</v>
       </c>
@@ -10498,13 +10485,13 @@
       <c r="I213" s="8"/>
     </row>
     <row r="214" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="15"/>
+      <c r="A214" s="22"/>
       <c r="B214" s="9"/>
       <c r="C214" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D214" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
@@ -10513,8 +10500,8 @@
       <c r="I214" s="11"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="20" t="s">
-        <v>533</v>
+      <c r="A215" s="21" t="s">
+        <v>359</v>
       </c>
       <c r="B215" s="6"/>
       <c r="C215" s="7">
@@ -10530,13 +10517,13 @@
       <c r="I215" s="8"/>
     </row>
     <row r="216" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="15"/>
+      <c r="A216" s="22"/>
       <c r="B216" s="9"/>
       <c r="C216" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D216" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
@@ -10545,12 +10532,10 @@
       <c r="I216" s="11"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>536</v>
-      </c>
+      <c r="A217" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="B217" s="6"/>
       <c r="C217" s="7">
         <v>250</v>
       </c>
@@ -10564,13 +10549,13 @@
       <c r="I217" s="8"/>
     </row>
     <row r="218" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="15"/>
+      <c r="A218" s="22"/>
       <c r="B218" s="9"/>
       <c r="C218" s="10" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D218" s="10" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -10579,10 +10564,12 @@
       <c r="I218" s="11"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="B219" s="6"/>
+      <c r="A219" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>536</v>
+      </c>
       <c r="C219" s="7">
         <v>250</v>
       </c>
@@ -10596,13 +10583,13 @@
       <c r="I219" s="8"/>
     </row>
     <row r="220" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="15"/>
+      <c r="A220" s="22"/>
       <c r="B220" s="9"/>
       <c r="C220" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -10611,8 +10598,8 @@
       <c r="I220" s="11"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="20" t="s">
-        <v>431</v>
+      <c r="A221" s="21" t="s">
+        <v>538</v>
       </c>
       <c r="B221" s="6"/>
       <c r="C221" s="7">
@@ -10628,13 +10615,13 @@
       <c r="I221" s="8"/>
     </row>
     <row r="222" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="15"/>
+      <c r="A222" s="22"/>
       <c r="B222" s="9"/>
       <c r="C222" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D222" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -10643,8 +10630,8 @@
       <c r="I222" s="11"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="20" t="s">
-        <v>413</v>
+      <c r="A223" s="21" t="s">
+        <v>431</v>
       </c>
       <c r="B223" s="6"/>
       <c r="C223" s="7">
@@ -10660,13 +10647,13 @@
       <c r="I223" s="8"/>
     </row>
     <row r="224" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="15"/>
+      <c r="A224" s="22"/>
       <c r="B224" s="9"/>
       <c r="C224" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D224" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -10675,8 +10662,8 @@
       <c r="I224" s="11"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="20" t="s">
-        <v>542</v>
+      <c r="A225" s="21" t="s">
+        <v>413</v>
       </c>
       <c r="B225" s="6"/>
       <c r="C225" s="7">
@@ -10692,7 +10679,7 @@
       <c r="I225" s="8"/>
     </row>
     <row r="226" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="15"/>
+      <c r="A226" s="22"/>
       <c r="B226" s="9"/>
       <c r="C226" s="10" t="s">
         <v>541</v>
@@ -10707,8 +10694,8 @@
       <c r="I226" s="11"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="20" t="s">
-        <v>543</v>
+      <c r="A227" s="21" t="s">
+        <v>542</v>
       </c>
       <c r="B227" s="6"/>
       <c r="C227" s="7">
@@ -10724,13 +10711,13 @@
       <c r="I227" s="8"/>
     </row>
     <row r="228" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="15"/>
+      <c r="A228" s="22"/>
       <c r="B228" s="9"/>
       <c r="C228" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
@@ -10739,8 +10726,8 @@
       <c r="I228" s="11"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="20" t="s">
-        <v>545</v>
+      <c r="A229" s="21" t="s">
+        <v>543</v>
       </c>
       <c r="B229" s="6"/>
       <c r="C229" s="7">
@@ -10756,13 +10743,13 @@
       <c r="I229" s="8"/>
     </row>
     <row r="230" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="15"/>
+      <c r="A230" s="22"/>
       <c r="B230" s="9"/>
       <c r="C230" s="10" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D230" s="10" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -10771,12 +10758,12 @@
       <c r="I230" s="11"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="20" t="s">
-        <v>547</v>
+      <c r="A231" s="21" t="s">
+        <v>545</v>
       </c>
       <c r="B231" s="6"/>
       <c r="C231" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D231" s="7">
         <v>1500</v>
@@ -10788,13 +10775,13 @@
       <c r="I231" s="8"/>
     </row>
     <row r="232" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="15"/>
+      <c r="A232" s="22"/>
       <c r="B232" s="9"/>
       <c r="C232" s="10" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
@@ -10803,12 +10790,12 @@
       <c r="I232" s="11"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A233" s="20" t="s">
-        <v>549</v>
+      <c r="A233" s="21" t="s">
+        <v>547</v>
       </c>
       <c r="B233" s="6"/>
       <c r="C233" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D233" s="7">
         <v>1500</v>
@@ -10820,13 +10807,13 @@
       <c r="I233" s="8"/>
     </row>
     <row r="234" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="15"/>
+      <c r="A234" s="22"/>
       <c r="B234" s="9"/>
       <c r="C234" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D234" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
@@ -10835,14 +10822,16 @@
       <c r="I234" s="11"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="20" t="s">
-        <v>551</v>
+      <c r="A235" s="21" t="s">
+        <v>549</v>
       </c>
       <c r="B235" s="6"/>
       <c r="C235" s="7">
         <v>250</v>
       </c>
-      <c r="D235" s="7"/>
+      <c r="D235" s="7">
+        <v>1500</v>
+      </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
       <c r="G235" s="8"/>
@@ -10850,12 +10839,14 @@
       <c r="I235" s="8"/>
     </row>
     <row r="236" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="15"/>
+      <c r="A236" s="22"/>
       <c r="B236" s="9"/>
       <c r="C236" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="D236" s="10"/>
+        <v>550</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>550</v>
+      </c>
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
       <c r="G236" s="11"/>
@@ -10863,8 +10854,8 @@
       <c r="I236" s="11"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="20" t="s">
-        <v>326</v>
+      <c r="A237" s="21" t="s">
+        <v>551</v>
       </c>
       <c r="B237" s="6"/>
       <c r="C237" s="7">
@@ -10877,11 +10868,11 @@
       <c r="H237" s="8"/>
       <c r="I237" s="8"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="15"/>
+    <row r="238" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="22"/>
       <c r="B238" s="9"/>
       <c r="C238" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D238" s="10"/>
       <c r="E238" s="10"/>
@@ -10890,42 +10881,109 @@
       <c r="H238" s="11"/>
       <c r="I238" s="11"/>
     </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B239" s="6"/>
+      <c r="C239" s="7">
+        <v>250</v>
+      </c>
+      <c r="D239" s="7"/>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="8"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="22"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="D240" s="10"/>
+      <c r="E240" s="10"/>
+      <c r="F240" s="10"/>
+      <c r="G240" s="11"/>
+      <c r="H240" s="11"/>
+      <c r="I240" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="116">
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="A225:A226"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="A197:I197"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A187:I187"/>
-    <mergeCell ref="A188:I188"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="A196:I196"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A180:I180"/>
-    <mergeCell ref="A181:I181"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
+  <mergeCells count="117">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A117:I117"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
     <mergeCell ref="A158:A159"/>
     <mergeCell ref="A160:A161"/>
     <mergeCell ref="A162:A163"/>
@@ -10936,78 +10994,40 @@
     <mergeCell ref="A152:A153"/>
     <mergeCell ref="A154:A155"/>
     <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A105:I105"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A187:I187"/>
+    <mergeCell ref="A188:I188"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="A198:I198"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A180:I180"/>
+    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="A199:I199"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A239:A240"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="A225:A226"/>
+    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -11026,30 +11046,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>554</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -11079,7 +11099,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>555</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -11098,7 +11118,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>557</v>
@@ -11113,7 +11133,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -11132,7 +11152,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
@@ -11145,7 +11165,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>563</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -11164,7 +11184,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>565</v>
@@ -11179,7 +11199,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>566</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -11198,7 +11218,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>568</v>
@@ -11213,7 +11233,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>569</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -11232,7 +11252,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>571</v>
@@ -11247,7 +11267,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>572</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -11266,7 +11286,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>574</v>
@@ -11281,7 +11301,7 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="23" t="s">
         <v>576</v>
       </c>
       <c r="B16" s="12"/>
@@ -11298,7 +11318,7 @@
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10" t="s">
         <v>577</v>
@@ -11313,28 +11333,28 @@
       <c r="I17" s="11"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>578</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -11366,7 +11386,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>579</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -11385,7 +11405,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="9"/>
       <c r="C24" s="10" t="s">
         <v>557</v>
@@ -11400,7 +11420,7 @@
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="23" t="s">
         <v>581</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -11419,7 +11439,7 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10" t="s">
         <v>583</v>
@@ -11434,7 +11454,7 @@
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="23" t="s">
         <v>584</v>
       </c>
       <c r="B27" s="12"/>
@@ -11451,7 +11471,7 @@
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>585</v>
@@ -11466,7 +11486,7 @@
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B29" s="12"/>
@@ -11483,7 +11503,7 @@
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10" t="s">
         <v>562</v>
@@ -11498,7 +11518,7 @@
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="23" t="s">
         <v>586</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -11517,7 +11537,7 @@
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10" t="s">
         <v>588</v>
@@ -11532,7 +11552,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="23" t="s">
         <v>589</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -11551,7 +11571,7 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10" t="s">
         <v>591</v>
@@ -11566,7 +11586,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="23" t="s">
         <v>576</v>
       </c>
       <c r="B35" s="12"/>
@@ -11583,7 +11603,7 @@
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9"/>
       <c r="C36" s="10" t="s">
         <v>577</v>
@@ -11598,7 +11618,7 @@
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="23" t="s">
         <v>572</v>
       </c>
       <c r="B37" s="12"/>
@@ -11615,7 +11635,7 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10" t="s">
         <v>592</v>
@@ -11630,7 +11650,7 @@
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="23" t="s">
         <v>593</v>
       </c>
       <c r="B39" s="12"/>
@@ -11647,7 +11667,7 @@
       <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>594</v>
@@ -11662,7 +11682,7 @@
       <c r="I40" s="11"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="23" t="s">
         <v>595</v>
       </c>
       <c r="B41" s="12"/>
@@ -11679,7 +11699,7 @@
       <c r="I41" s="11"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="9"/>
       <c r="C42" s="10" t="s">
         <v>596</v>
@@ -11694,7 +11714,7 @@
       <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="23" t="s">
         <v>597</v>
       </c>
       <c r="B43" s="12"/>
@@ -11711,7 +11731,7 @@
       <c r="I43" s="11"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="9"/>
       <c r="C44" s="10" t="s">
         <v>598</v>
@@ -11726,7 +11746,7 @@
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="23" t="s">
         <v>599</v>
       </c>
       <c r="B45" s="12"/>
@@ -11743,7 +11763,7 @@
       <c r="I45" s="11"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="9"/>
       <c r="C46" s="10" t="s">
         <v>600</v>
@@ -11758,7 +11778,7 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="23" t="s">
         <v>601</v>
       </c>
       <c r="B47" s="12"/>
@@ -11775,7 +11795,7 @@
       <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="9"/>
       <c r="C48" s="10" t="s">
         <v>602</v>
@@ -11790,7 +11810,7 @@
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="23" t="s">
         <v>603</v>
       </c>
       <c r="B49" s="12"/>
@@ -11805,7 +11825,7 @@
       <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="9"/>
       <c r="C50" s="10" t="s">
         <v>602</v>
@@ -11818,7 +11838,7 @@
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="23" t="s">
         <v>604</v>
       </c>
       <c r="B51" s="12">
@@ -11837,7 +11857,7 @@
       <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="9"/>
       <c r="C52" s="10" t="s">
         <v>605</v>
@@ -11852,28 +11872,28 @@
       <c r="I52" s="11"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
     </row>
     <row r="56" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>606</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="19"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="20"/>
     </row>
     <row r="57" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
@@ -11905,7 +11925,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="21" t="s">
         <v>559</v>
       </c>
       <c r="B58" s="6"/>
@@ -11922,7 +11942,7 @@
       <c r="I58" s="8"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="9"/>
       <c r="C59" s="10" t="s">
         <v>562</v>
@@ -11937,7 +11957,7 @@
       <c r="I59" s="11"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="23" t="s">
         <v>607</v>
       </c>
       <c r="B60" s="12"/>
@@ -11954,7 +11974,7 @@
       <c r="I60" s="11"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="9"/>
       <c r="C61" s="10" t="s">
         <v>608</v>
@@ -11969,28 +11989,28 @@
       <c r="I61" s="11"/>
     </row>
     <row r="64" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="16"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
     </row>
     <row r="65" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="18" t="s">
         <v>609</v>
       </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="19"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="20"/>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
@@ -12022,7 +12042,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="21" t="s">
         <v>584</v>
       </c>
       <c r="B67" s="6"/>
@@ -12039,7 +12059,7 @@
       <c r="I67" s="8"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="9"/>
       <c r="C68" s="10" t="s">
         <v>585</v>
@@ -12054,7 +12074,7 @@
       <c r="I68" s="11"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="23" t="s">
         <v>610</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -12073,7 +12093,7 @@
       <c r="I69" s="11"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="9"/>
       <c r="C70" s="10" t="s">
         <v>612</v>
@@ -12088,7 +12108,7 @@
       <c r="I70" s="11"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B71" s="12"/>
@@ -12105,7 +12125,7 @@
       <c r="I71" s="11"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
         <v>562</v>
@@ -12120,7 +12140,7 @@
       <c r="I72" s="11"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="23" t="s">
         <v>613</v>
       </c>
       <c r="B73" s="12"/>
@@ -12135,7 +12155,7 @@
       <c r="I73" s="11"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="15"/>
+      <c r="A74" s="22"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
         <v>614</v>
@@ -12148,7 +12168,7 @@
       <c r="I74" s="11"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="23" t="s">
         <v>615</v>
       </c>
       <c r="B75" s="12" t="s">
@@ -12167,7 +12187,7 @@
       <c r="I75" s="11"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
+      <c r="A76" s="22"/>
       <c r="B76" s="9"/>
       <c r="C76" s="10" t="s">
         <v>617</v>
@@ -12182,7 +12202,7 @@
       <c r="I76" s="11"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="23" t="s">
         <v>589</v>
       </c>
       <c r="B77" s="12" t="s">
@@ -12201,7 +12221,7 @@
       <c r="I77" s="11"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="15"/>
+      <c r="A78" s="22"/>
       <c r="B78" s="9"/>
       <c r="C78" s="10" t="s">
         <v>591</v>
@@ -12216,7 +12236,7 @@
       <c r="I78" s="11"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="23" t="s">
         <v>618</v>
       </c>
       <c r="B79" s="12" t="s">
@@ -12235,7 +12255,7 @@
       <c r="I79" s="11"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="9"/>
       <c r="C80" s="10" t="s">
         <v>591</v>
@@ -12250,7 +12270,7 @@
       <c r="I80" s="11"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="23" t="s">
         <v>607</v>
       </c>
       <c r="B81" s="12"/>
@@ -12267,7 +12287,7 @@
       <c r="I81" s="11"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="15"/>
+      <c r="A82" s="22"/>
       <c r="B82" s="9"/>
       <c r="C82" s="10" t="s">
         <v>620</v>
@@ -12282,7 +12302,7 @@
       <c r="I82" s="11"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="23" t="s">
         <v>621</v>
       </c>
       <c r="B83" s="12"/>
@@ -12299,7 +12319,7 @@
       <c r="I83" s="11"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="15"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="9"/>
       <c r="C84" s="10" t="s">
         <v>622</v>
@@ -12314,7 +12334,7 @@
       <c r="I84" s="11"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="23" t="s">
         <v>623</v>
       </c>
       <c r="B85" s="12"/>
@@ -12331,7 +12351,7 @@
       <c r="I85" s="11"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="15"/>
+      <c r="A86" s="22"/>
       <c r="B86" s="9"/>
       <c r="C86" s="10" t="s">
         <v>624</v>
@@ -12346,7 +12366,7 @@
       <c r="I86" s="11"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="23" t="s">
         <v>625</v>
       </c>
       <c r="B87" s="12"/>
@@ -12363,7 +12383,7 @@
       <c r="I87" s="11"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="9"/>
       <c r="C88" s="10" t="s">
         <v>626</v>
@@ -12378,7 +12398,7 @@
       <c r="I88" s="11"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="23" t="s">
         <v>627</v>
       </c>
       <c r="B89" s="12"/>
@@ -12395,7 +12415,7 @@
       <c r="I89" s="11"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="15"/>
+      <c r="A90" s="22"/>
       <c r="B90" s="9"/>
       <c r="C90" s="10" t="s">
         <v>628</v>
@@ -12411,6 +12431,42 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="A89:A90"/>
     <mergeCell ref="A75:A76"/>
@@ -12419,42 +12475,6 @@
     <mergeCell ref="A81:A82"/>
     <mergeCell ref="A83:A84"/>
     <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12472,30 +12492,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -12525,7 +12545,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>630</v>
       </c>
       <c r="B4" s="6"/>
@@ -12540,7 +12560,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
@@ -12553,7 +12573,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>632</v>
       </c>
       <c r="B6" s="12"/>
@@ -12570,7 +12590,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>633</v>
@@ -12585,7 +12605,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>634</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -12604,7 +12624,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>636</v>
@@ -12619,7 +12639,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>637</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -12638,7 +12658,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>639</v>
@@ -12653,7 +12673,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>641</v>
       </c>
       <c r="B12" s="12"/>
@@ -12670,7 +12690,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>642</v>
@@ -12685,7 +12705,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>643</v>
       </c>
       <c r="B14" s="12"/>
@@ -12702,7 +12722,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>644</v>
@@ -12717,28 +12737,28 @@
       <c r="I15" s="11"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -12770,7 +12790,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="21" t="s">
         <v>630</v>
       </c>
       <c r="B21" s="6"/>
@@ -12785,7 +12805,7 @@
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
@@ -12798,28 +12818,28 @@
       <c r="I22" s="11"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -12851,7 +12871,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="21" t="s">
         <v>647</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -12870,7 +12890,7 @@
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10" t="s">
         <v>649</v>
@@ -12885,7 +12905,7 @@
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="23" t="s">
         <v>650</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -12904,7 +12924,7 @@
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="9"/>
       <c r="C31" s="10" t="s">
         <v>652</v>
@@ -12919,28 +12939,28 @@
       <c r="I31" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -12972,7 +12992,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="21" t="s">
         <v>654</v>
       </c>
       <c r="B37" s="6"/>
@@ -12989,7 +13009,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10" t="s">
         <v>655</v>
@@ -13005,6 +13025,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:I26"/>
@@ -13012,17 +13043,6 @@
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13040,30 +13060,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>656</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -13093,7 +13113,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>657</v>
       </c>
       <c r="B4" s="6"/>
@@ -13110,7 +13130,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>658</v>
@@ -13125,7 +13145,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>659</v>
       </c>
       <c r="B6" s="12"/>
@@ -13142,7 +13162,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>660</v>
@@ -13157,28 +13177,28 @@
       <c r="I7" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>661</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -13210,7 +13230,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>662</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -13229,7 +13249,7 @@
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="9"/>
       <c r="C14" s="10" t="s">
         <v>664</v>
@@ -13268,30 +13288,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>665</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -13321,7 +13341,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>666</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -13338,7 +13358,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
@@ -13351,7 +13371,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>669</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -13370,7 +13390,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>671</v>
@@ -13385,7 +13405,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>673</v>
       </c>
       <c r="B8" s="12"/>
@@ -13402,7 +13422,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>674</v>
@@ -13417,7 +13437,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>675</v>
       </c>
       <c r="B10" s="12"/>
@@ -13434,7 +13454,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>676</v>
@@ -13449,7 +13469,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>677</v>
       </c>
       <c r="B12" s="12"/>
@@ -13466,7 +13486,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>678</v>
@@ -13481,7 +13501,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>679</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -13500,7 +13520,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>681</v>
@@ -13515,7 +13535,7 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="23" t="s">
         <v>682</v>
       </c>
       <c r="B16" s="12"/>
@@ -13532,7 +13552,7 @@
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10" t="s">
         <v>683</v>
@@ -13547,7 +13567,7 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="23" t="s">
         <v>684</v>
       </c>
       <c r="B18" s="12"/>
@@ -13564,7 +13584,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10" t="s">
         <v>685</v>
@@ -13579,7 +13599,7 @@
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="23" t="s">
         <v>686</v>
       </c>
       <c r="B20" s="12"/>
@@ -13596,7 +13616,7 @@
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10" t="s">
         <v>687</v>
@@ -13611,7 +13631,7 @@
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="23" t="s">
         <v>688</v>
       </c>
       <c r="B22" s="12"/>
@@ -13628,7 +13648,7 @@
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10" t="s">
         <v>689</v>
@@ -13643,7 +13663,7 @@
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="23" t="s">
         <v>690</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -13662,7 +13682,7 @@
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10" t="s">
         <v>692</v>
@@ -13677,7 +13697,7 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="23" t="s">
         <v>693</v>
       </c>
       <c r="B26" s="12"/>
@@ -13692,7 +13712,7 @@
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
       <c r="D27" s="10" t="s">
@@ -13705,7 +13725,7 @@
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="23" t="s">
         <v>695</v>
       </c>
       <c r="B28" s="12"/>
@@ -13722,7 +13742,7 @@
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10" t="s">
         <v>696</v>
@@ -13737,7 +13757,7 @@
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="23" t="s">
         <v>697</v>
       </c>
       <c r="B30" s="12"/>
@@ -13754,7 +13774,7 @@
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="9"/>
       <c r="C31" s="10" t="s">
         <v>698</v>
@@ -13769,7 +13789,7 @@
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="23" t="s">
         <v>699</v>
       </c>
       <c r="B32" s="12"/>
@@ -13786,7 +13806,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="9"/>
       <c r="C33" s="10" t="s">
         <v>700</v>
@@ -13801,7 +13821,7 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="23" t="s">
         <v>702</v>
       </c>
       <c r="B34" s="12"/>
@@ -13816,7 +13836,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10" t="s">
@@ -13829,7 +13849,7 @@
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="23" t="s">
         <v>704</v>
       </c>
       <c r="B36" s="12"/>
@@ -13846,7 +13866,7 @@
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="9"/>
       <c r="C37" s="10" t="s">
         <v>705</v>
@@ -13861,7 +13881,7 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="23" t="s">
         <v>706</v>
       </c>
       <c r="B38" s="12"/>
@@ -13878,7 +13898,7 @@
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10" t="s">
         <v>707</v>
@@ -13893,28 +13913,28 @@
       <c r="I39" s="11"/>
     </row>
     <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
     </row>
     <row r="43" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>708</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
@@ -13946,7 +13966,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="21" t="s">
         <v>666</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -13965,7 +13985,7 @@
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="9"/>
       <c r="C46" s="10" t="s">
         <v>668</v>
@@ -13980,7 +14000,7 @@
       <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="23" t="s">
         <v>669</v>
       </c>
       <c r="B47" s="12" t="s">
@@ -13999,7 +14019,7 @@
       <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="9"/>
       <c r="C48" s="10" t="s">
         <v>716</v>
@@ -14014,7 +14034,7 @@
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="23" t="s">
         <v>673</v>
       </c>
       <c r="B49" s="12" t="s">
@@ -14033,7 +14053,7 @@
       <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="9"/>
       <c r="C50" s="10" t="s">
         <v>674</v>
@@ -14048,7 +14068,7 @@
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="23" t="s">
         <v>675</v>
       </c>
       <c r="B51" s="12"/>
@@ -14065,7 +14085,7 @@
       <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="9"/>
       <c r="C52" s="10" t="s">
         <v>676</v>
@@ -14080,7 +14100,7 @@
       <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="23" t="s">
         <v>677</v>
       </c>
       <c r="B53" s="12" t="s">
@@ -14099,7 +14119,7 @@
       <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="9"/>
       <c r="C54" s="10" t="s">
         <v>678</v>
@@ -14114,7 +14134,7 @@
       <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="23" t="s">
         <v>679</v>
       </c>
       <c r="B55" s="12" t="s">
@@ -14133,7 +14153,7 @@
       <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="9"/>
       <c r="C56" s="10" t="s">
         <v>681</v>
@@ -14148,7 +14168,7 @@
       <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="23" t="s">
         <v>682</v>
       </c>
       <c r="B57" s="12"/>
@@ -14165,7 +14185,7 @@
       <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="9"/>
       <c r="C58" s="10" t="s">
         <v>683</v>
@@ -14180,7 +14200,7 @@
       <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="23" t="s">
         <v>684</v>
       </c>
       <c r="B59" s="12"/>
@@ -14197,7 +14217,7 @@
       <c r="I59" s="11"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="15"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="9"/>
       <c r="C60" s="10" t="s">
         <v>685</v>
@@ -14212,7 +14232,7 @@
       <c r="I60" s="11"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="23" t="s">
         <v>686</v>
       </c>
       <c r="B61" s="12"/>
@@ -14229,7 +14249,7 @@
       <c r="I61" s="11"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="15"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="9"/>
       <c r="C62" s="10" t="s">
         <v>717</v>
@@ -14244,7 +14264,7 @@
       <c r="I62" s="11"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="23" t="s">
         <v>688</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -14263,7 +14283,7 @@
       <c r="I63" s="11"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="15"/>
+      <c r="A64" s="22"/>
       <c r="B64" s="9"/>
       <c r="C64" s="10" t="s">
         <v>718</v>
@@ -14278,7 +14298,7 @@
       <c r="I64" s="11"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="23" t="s">
         <v>690</v>
       </c>
       <c r="B65" s="12" t="s">
@@ -14297,7 +14317,7 @@
       <c r="I65" s="11"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="15"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="9"/>
       <c r="C66" s="10" t="s">
         <v>719</v>
@@ -14312,7 +14332,7 @@
       <c r="I66" s="11"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="23" t="s">
         <v>693</v>
       </c>
       <c r="B67" s="12"/>
@@ -14327,7 +14347,7 @@
       <c r="I67" s="11"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="9"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10" t="s">
@@ -14340,7 +14360,7 @@
       <c r="I68" s="11"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="23" t="s">
         <v>695</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -14359,7 +14379,7 @@
       <c r="I69" s="11"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="9"/>
       <c r="C70" s="10" t="s">
         <v>720</v>
@@ -14374,7 +14394,7 @@
       <c r="I70" s="11"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="23" t="s">
         <v>697</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -14393,7 +14413,7 @@
       <c r="I71" s="11"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
         <v>698</v>
@@ -14408,7 +14428,7 @@
       <c r="I72" s="11"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="23" t="s">
         <v>699</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -14427,7 +14447,7 @@
       <c r="I73" s="11"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="15"/>
+      <c r="A74" s="22"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
         <v>700</v>
@@ -14442,7 +14462,7 @@
       <c r="I74" s="11"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="23" t="s">
         <v>702</v>
       </c>
       <c r="B75" s="12"/>
@@ -14457,7 +14477,7 @@
       <c r="I75" s="11"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
+      <c r="A76" s="22"/>
       <c r="B76" s="9"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10" t="s">
@@ -14470,7 +14490,7 @@
       <c r="I76" s="11"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="23" t="s">
         <v>709</v>
       </c>
       <c r="B77" s="12"/>
@@ -14487,7 +14507,7 @@
       <c r="I77" s="11"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="15"/>
+      <c r="A78" s="22"/>
       <c r="B78" s="9"/>
       <c r="C78" s="10" t="s">
         <v>707</v>
@@ -14502,7 +14522,7 @@
       <c r="I78" s="11"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="23" t="s">
         <v>704</v>
       </c>
       <c r="B79" s="12"/>
@@ -14517,7 +14537,7 @@
       <c r="I79" s="11"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="9"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10" t="s">
@@ -14530,28 +14550,28 @@
       <c r="I80" s="11"/>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="16"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
-      <c r="H82" s="16"/>
-      <c r="I82" s="16"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
     </row>
     <row r="83" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="17" t="s">
+      <c r="A83" s="18" t="s">
         <v>722</v>
       </c>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="19"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="20"/>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
@@ -14583,7 +14603,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="20" t="s">
+      <c r="A85" s="21" t="s">
         <v>666</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -14602,7 +14622,7 @@
       <c r="I85" s="8"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="15"/>
+      <c r="A86" s="22"/>
       <c r="B86" s="9"/>
       <c r="C86" s="10" t="s">
         <v>668</v>
@@ -14617,7 +14637,7 @@
       <c r="I86" s="11"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="23" t="s">
         <v>684</v>
       </c>
       <c r="B87" s="12"/>
@@ -14634,7 +14654,7 @@
       <c r="I87" s="11"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="9"/>
       <c r="C88" s="10" t="s">
         <v>723</v>
@@ -14649,7 +14669,7 @@
       <c r="I88" s="11"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="23" t="s">
         <v>724</v>
       </c>
       <c r="B89" s="12" t="s">
@@ -14668,7 +14688,7 @@
       <c r="I89" s="11"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="15"/>
+      <c r="A90" s="22"/>
       <c r="B90" s="9"/>
       <c r="C90" s="10" t="s">
         <v>726</v>
@@ -14683,7 +14703,7 @@
       <c r="I90" s="11"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="23" t="s">
         <v>727</v>
       </c>
       <c r="B91" s="12"/>
@@ -14700,7 +14720,7 @@
       <c r="I91" s="11"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
+      <c r="A92" s="22"/>
       <c r="B92" s="9"/>
       <c r="C92" s="10" t="s">
         <v>728</v>
@@ -14715,7 +14735,7 @@
       <c r="I92" s="11"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="23" t="s">
         <v>729</v>
       </c>
       <c r="B93" s="12"/>
@@ -14732,7 +14752,7 @@
       <c r="I93" s="11"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="15"/>
+      <c r="A94" s="22"/>
       <c r="B94" s="9"/>
       <c r="C94" s="10" t="s">
         <v>730</v>
@@ -14747,7 +14767,7 @@
       <c r="I94" s="11"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="23" t="s">
         <v>731</v>
       </c>
       <c r="B95" s="12"/>
@@ -14764,7 +14784,7 @@
       <c r="I95" s="11"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="9"/>
       <c r="C96" s="10" t="s">
         <v>732</v>
@@ -14779,7 +14799,7 @@
       <c r="I96" s="11"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="23" t="s">
         <v>702</v>
       </c>
       <c r="B97" s="12"/>
@@ -14794,7 +14814,7 @@
       <c r="I97" s="11"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
+      <c r="A98" s="22"/>
       <c r="B98" s="9"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10" t="s">
@@ -14807,7 +14827,7 @@
       <c r="I98" s="11"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="23" t="s">
         <v>734</v>
       </c>
       <c r="B99" s="12"/>
@@ -14824,7 +14844,7 @@
       <c r="I99" s="11"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="9"/>
       <c r="C100" s="10" t="s">
         <v>735</v>
@@ -14839,28 +14859,28 @@
       <c r="I100" s="11"/>
     </row>
     <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="16"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="16"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="16"/>
-      <c r="H103" s="16"/>
-      <c r="I103" s="16"/>
+      <c r="A103" s="17"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
     </row>
     <row r="104" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="18" t="s">
         <v>736</v>
       </c>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="18"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="18"/>
-      <c r="G104" s="18"/>
-      <c r="H104" s="18"/>
-      <c r="I104" s="19"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="19"/>
+      <c r="D104" s="19"/>
+      <c r="E104" s="19"/>
+      <c r="F104" s="19"/>
+      <c r="G104" s="19"/>
+      <c r="H104" s="19"/>
+      <c r="I104" s="20"/>
     </row>
     <row r="105" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
@@ -14892,7 +14912,7 @@
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="21" t="s">
         <v>666</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -14911,7 +14931,7 @@
       <c r="I106" s="8"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="22"/>
       <c r="B107" s="9"/>
       <c r="C107" s="10" t="s">
         <v>668</v>
@@ -14926,7 +14946,7 @@
       <c r="I107" s="11"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="23" t="s">
         <v>737</v>
       </c>
       <c r="B108" s="12" t="s">
@@ -14945,7 +14965,7 @@
       <c r="I108" s="11"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="22"/>
       <c r="B109" s="9"/>
       <c r="C109" s="10" t="s">
         <v>671</v>
@@ -14960,7 +14980,7 @@
       <c r="I109" s="11"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="23" t="s">
         <v>684</v>
       </c>
       <c r="B110" s="12"/>
@@ -14975,7 +14995,7 @@
       <c r="I110" s="11"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="22"/>
       <c r="B111" s="9"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10" t="s">
@@ -14988,7 +15008,7 @@
       <c r="I111" s="11"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="23" t="s">
         <v>740</v>
       </c>
       <c r="B112" s="12"/>
@@ -15003,7 +15023,7 @@
       <c r="I112" s="11"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="22"/>
       <c r="B113" s="9"/>
       <c r="C113" s="10" t="s">
         <v>700</v>
@@ -15016,7 +15036,7 @@
       <c r="I113" s="11"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="23" t="s">
         <v>741</v>
       </c>
       <c r="B114" s="12"/>
@@ -15033,7 +15053,7 @@
       <c r="I114" s="11"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="22"/>
       <c r="B115" s="9"/>
       <c r="C115" s="10" t="s">
         <v>742</v>
@@ -15048,7 +15068,7 @@
       <c r="I115" s="11"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="23" t="s">
         <v>743</v>
       </c>
       <c r="B116" s="12"/>
@@ -15065,7 +15085,7 @@
       <c r="I116" s="11"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="22"/>
       <c r="B117" s="9"/>
       <c r="C117" s="10" t="s">
         <v>744</v>
@@ -15081,6 +15101,56 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
     <mergeCell ref="A114:A115"/>
     <mergeCell ref="A116:A117"/>
     <mergeCell ref="A103:I103"/>
@@ -15089,56 +15159,6 @@
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="A110:A111"/>
     <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15156,30 +15176,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>745</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -15209,7 +15229,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>746</v>
       </c>
       <c r="B4" s="6"/>
@@ -15224,7 +15244,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>747</v>
@@ -15237,7 +15257,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>748</v>
       </c>
       <c r="B6" s="12"/>
@@ -15252,7 +15272,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>749</v>
@@ -15265,7 +15285,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>750</v>
       </c>
       <c r="B8" s="12"/>
@@ -15280,7 +15300,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>751</v>
@@ -15293,7 +15313,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>752</v>
       </c>
       <c r="B10" s="12"/>
@@ -15310,7 +15330,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>753</v>
@@ -15325,7 +15345,7 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="23" t="s">
         <v>754</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -15344,7 +15364,7 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>756</v>
@@ -15359,7 +15379,7 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="23" t="s">
         <v>757</v>
       </c>
       <c r="B14" s="12"/>
@@ -15376,7 +15396,7 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>758</v>
@@ -15391,7 +15411,7 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="23" t="s">
         <v>759</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -15408,7 +15428,7 @@
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
@@ -15421,7 +15441,7 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="23" t="s">
         <v>762</v>
       </c>
       <c r="B18" s="12"/>
@@ -15436,7 +15456,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
@@ -15449,7 +15469,7 @@
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="23" t="s">
         <v>764</v>
       </c>
       <c r="B20" s="12"/>
@@ -15466,7 +15486,7 @@
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10" t="s">
         <v>765</v>
@@ -15481,7 +15501,7 @@
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="23" t="s">
         <v>766</v>
       </c>
       <c r="B22" s="12"/>
@@ -15498,7 +15518,7 @@
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10" t="s">
         <v>767</v>
@@ -15513,7 +15533,7 @@
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="23" t="s">
         <v>768</v>
       </c>
       <c r="B24" s="12"/>
@@ -15530,7 +15550,7 @@
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10" t="s">
         <v>769</v>
@@ -15545,28 +15565,28 @@
       <c r="I25" s="11"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>770</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="20"/>
     </row>
     <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -15598,7 +15618,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="21" t="s">
         <v>752</v>
       </c>
       <c r="B31" s="6"/>
@@ -15615,7 +15635,7 @@
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10" t="s">
         <v>753</v>
@@ -15630,7 +15650,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="23" t="s">
         <v>754</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -15649,7 +15669,7 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10" t="s">
         <v>756</v>
@@ -15664,7 +15684,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="23" t="s">
         <v>757</v>
       </c>
       <c r="B35" s="12"/>
@@ -15681,7 +15701,7 @@
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9"/>
       <c r="C36" s="10" t="s">
         <v>758</v>
@@ -15696,7 +15716,7 @@
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="23" t="s">
         <v>762</v>
       </c>
       <c r="B37" s="12"/>
@@ -15711,7 +15731,7 @@
       <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10" t="s">
@@ -15724,7 +15744,7 @@
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="23" t="s">
         <v>764</v>
       </c>
       <c r="B39" s="12"/>
@@ -15741,7 +15761,7 @@
       <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>765</v>
@@ -15756,28 +15776,28 @@
       <c r="I40" s="11"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
     </row>
     <row r="44" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>771</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
@@ -15809,7 +15829,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="21" t="s">
         <v>754</v>
       </c>
       <c r="B46" s="6"/>
@@ -15826,7 +15846,7 @@
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="9"/>
       <c r="C47" s="10" t="s">
         <v>772</v>
@@ -15841,7 +15861,7 @@
       <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="23" t="s">
         <v>757</v>
       </c>
       <c r="B48" s="12"/>
@@ -15856,7 +15876,7 @@
       <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="9"/>
       <c r="C49" s="10" t="s">
         <v>773</v>
@@ -15869,7 +15889,7 @@
       <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="23" t="s">
         <v>774</v>
       </c>
       <c r="B50" s="12"/>
@@ -15886,7 +15906,7 @@
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="9"/>
       <c r="C51" s="10" t="s">
         <v>775</v>
@@ -15902,6 +15922,24 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="A39:A40"/>
@@ -15909,24 +15947,6 @@
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15944,30 +15964,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>776</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -15997,7 +16017,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>777</v>
       </c>
       <c r="B4" s="6"/>
@@ -16014,7 +16034,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
         <v>631</v>
@@ -16029,7 +16049,7 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>778</v>
       </c>
       <c r="B6" s="12"/>
@@ -16044,7 +16064,7 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
@@ -16057,7 +16077,7 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>780</v>
       </c>
       <c r="B8" s="12"/>
@@ -16074,7 +16094,7 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>781</v>
@@ -16089,7 +16109,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="23" t="s">
         <v>782</v>
       </c>
       <c r="B10" s="12"/>
@@ -16106,7 +16126,7 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10" t="s">
         <v>783</v>
@@ -16121,28 +16141,28 @@
       <c r="I11" s="11"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>784</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -16174,7 +16194,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="21" t="s">
         <v>777</v>
       </c>
       <c r="B17" s="6"/>
@@ -16191,7 +16211,7 @@
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="9"/>
       <c r="C18" s="10" t="s">
         <v>631</v>
@@ -16206,7 +16226,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="23" t="s">
         <v>778</v>
       </c>
       <c r="B19" s="12"/>
@@ -16223,7 +16243,7 @@
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="9"/>
       <c r="C20" s="10" t="s">
         <v>779</v>
